--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$82</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2800" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3059" uniqueCount="569">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -605,13 +605,7 @@
     <t>This is generally only used for "exception" statuses such as "suspended" or "cancelled". The reason why the MedicationRequest was created at all is captured in reasonCode, not here.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Identifies the reasons for a given status.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetPlaneintragStatusReasonVS</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -661,7 +655,7 @@
 </t>
   </si>
   <si>
-    <t>Keine codierte Begründung für den Status des Planeintrags.</t>
+    <t>Codierte Begründung für den Status des Planeintrags.</t>
   </si>
   <si>
     <t>A reference to a code defined by a terminology system.</t>
@@ -680,6 +674,127 @@
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>MedicationRequest.statusReason.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
   </si>
   <si>
     <t>MedicationRequest.statusReason.text</t>
@@ -761,6 +876,9 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
   </si>
   <si>
@@ -802,10 +920,6 @@
   </si>
   <si>
     <t>MedicationRequest.doNotPerform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>Arzneimittel, die (z.B. aufgrund einer Allergie) nicht eingenommen bzw. verordnet werden dürfen, werden nicht dokumentiert.</t>
@@ -2019,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO75"/>
+  <dimension ref="A1:AO82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -2047,7 +2161,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="138.53125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.75" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3769,13 +3883,11 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y15" s="2"/>
+      <c r="Z15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3808,13 +3920,13 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>21</v>
@@ -3825,10 +3937,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3851,13 +3963,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3908,7 +4020,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3929,7 +4041,7 @@
         <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>21</v>
@@ -3940,10 +4052,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3969,10 +4081,10 @@
         <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>159</v>
@@ -4016,7 +4128,7 @@
         <v>138</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
@@ -4025,7 +4137,7 @@
         <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4046,7 +4158,7 @@
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
@@ -4057,10 +4169,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4071,7 +4183,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -4083,19 +4195,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -4144,7 +4256,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4165,21 +4277,21 @@
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
+      <c r="A19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AN18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4193,29 +4305,25 @@
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>216</v>
-      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -4263,7 +4371,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4275,7 +4383,7 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
@@ -4284,53 +4392,53 @@
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>223</v>
+        <v>159</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4341,7 +4449,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -4356,66 +4464,66 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4423,33 +4531,35 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -4458,7 +4568,7 @@
         <v>21</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>21</v>
@@ -4473,13 +4583,13 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -4497,13 +4607,13 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -4515,24 +4625,24 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>21</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4543,7 +4653,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4555,15 +4665,17 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4588,13 +4700,13 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -4612,7 +4724,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4627,27 +4739,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4655,33 +4767,33 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>248</v>
+        <v>110</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4729,7 +4841,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4750,21 +4862,21 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4772,7 +4884,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
@@ -4787,16 +4899,18 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4832,17 +4946,19 @@
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4863,25 +4979,23 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4890,7 +5004,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4902,16 +5016,20 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4959,7 +5077,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4980,25 +5098,23 @@
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>21</v>
       </c>
@@ -5019,16 +5135,20 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -5076,7 +5196,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5097,21 +5217,21 @@
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5128,22 +5248,22 @@
         <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5154,7 +5274,7 @@
         <v>21</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>21</v>
@@ -5169,13 +5289,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5193,7 +5313,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -5208,27 +5328,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>275</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5248,19 +5368,19 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>277</v>
+        <v>183</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5271,7 +5391,7 @@
         <v>21</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>21</v>
@@ -5286,13 +5406,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5310,13 +5430,13 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -5325,27 +5445,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>285</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5365,20 +5485,18 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5403,13 +5521,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5427,7 +5545,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5442,27 +5560,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>294</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5479,21 +5597,23 @@
         <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5542,13 +5662,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5557,27 +5677,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5591,7 +5711,7 @@
         <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5600,13 +5720,13 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5645,19 +5765,17 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5672,41 +5790,43 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>309</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5715,13 +5835,13 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5772,7 +5892,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5787,29 +5907,31 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>314</v>
+        <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5818,25 +5940,25 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>317</v>
+        <v>242</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5887,7 +6009,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5902,27 +6024,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5930,13 +6052,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -5945,16 +6067,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>183</v>
+        <v>305</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5980,13 +6102,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -6004,10 +6126,10 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -6019,27 +6141,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>21</v>
+        <v>312</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>21</v>
+        <v>313</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6047,30 +6169,32 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6119,10 +6243,10 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>90</v>
@@ -6134,27 +6258,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6177,16 +6301,16 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>183</v>
+        <v>325</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6212,13 +6336,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -6236,13 +6360,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6251,27 +6375,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>344</v>
+        <v>179</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6294,17 +6418,15 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6353,7 +6475,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6368,27 +6490,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6396,13 +6518,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6411,13 +6533,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6468,13 +6590,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -6483,27 +6605,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6511,13 +6633,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6526,13 +6648,13 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>349</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6583,13 +6705,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6598,16 +6720,16 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>321</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6615,10 +6737,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6638,16 +6760,16 @@
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6698,13 +6820,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6713,16 +6835,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6730,10 +6852,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6756,18 +6878,18 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6791,13 +6913,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6815,7 +6937,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6830,13 +6952,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6845,12 +6967,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6858,13 +6980,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6873,17 +6995,15 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>183</v>
+        <v>370</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6908,13 +7028,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>381</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6932,7 +7052,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6953,10 +7073,10 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -6964,10 +7084,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6990,15 +7110,17 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>384</v>
+        <v>183</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7023,13 +7145,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>21</v>
+        <v>380</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -7047,7 +7169,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7062,27 +7184,27 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7093,10 +7215,10 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7105,15 +7227,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7162,7 +7286,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7177,16 +7301,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>394</v>
-      </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -7194,10 +7318,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7205,32 +7329,30 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K45" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L45" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>399</v>
-      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7267,17 +7389,19 @@
         <v>21</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7292,13 +7416,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7307,16 +7431,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7325,29 +7447,27 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K46" t="s" s="2">
-        <v>405</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7396,7 +7516,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7411,31 +7531,29 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="B47" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7444,29 +7562,27 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K47" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7515,7 +7631,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7530,13 +7646,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7545,16 +7661,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7563,30 +7677,30 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>412</v>
+        <v>163</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7634,13 +7748,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7649,13 +7763,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7666,23 +7780,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C49" t="s" s="2">
         <v>414</v>
       </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>91</v>
@@ -7694,16 +7806,16 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="L49" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="M49" t="s" s="2">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7729,13 +7841,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7753,13 +7865,13 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
@@ -7768,13 +7880,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7783,16 +7895,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7801,10 +7911,10 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7813,17 +7923,15 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7872,7 +7980,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7887,13 +7995,13 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7902,12 +8010,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7918,10 +8026,10 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -7930,13 +8038,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7987,13 +8095,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8002,13 +8110,13 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8019,10 +8127,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8030,13 +8138,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
@@ -8045,15 +8153,17 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>193</v>
+        <v>434</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>194</v>
+        <v>435</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8090,40 +8200,38 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>196</v>
+        <v>433</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>197</v>
+        <v>440</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8132,16 +8240,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="D53" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8151,7 +8261,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -8160,16 +8270,16 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>443</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>199</v>
+        <v>444</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>200</v>
+        <v>436</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>159</v>
+        <v>437</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8219,7 +8329,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>202</v>
+        <v>433</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8231,16 +8341,16 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>197</v>
+        <v>440</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8249,16 +8359,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="D54" t="s" s="2">
-        <v>428</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8268,29 +8380,27 @@
         <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>447</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8338,7 +8448,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8350,16 +8460,16 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>133</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8368,14 +8478,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8384,10 +8496,10 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8396,16 +8508,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8455,13 +8567,13 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
@@ -8470,13 +8582,13 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8485,14 +8597,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8501,10 +8615,10 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -8513,15 +8627,17 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>193</v>
+        <v>453</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>194</v>
+        <v>444</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8570,28 +8686,28 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>196</v>
+        <v>433</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>197</v>
+        <v>440</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8600,16 +8716,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8619,7 +8737,7 @@
         <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8628,16 +8746,16 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>456</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>199</v>
+        <v>444</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>200</v>
+        <v>436</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>159</v>
+        <v>437</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8687,7 +8805,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>202</v>
+        <v>433</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8699,16 +8817,16 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>197</v>
+        <v>440</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8719,46 +8837,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>428</v>
+        <v>21</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>458</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8806,28 +8920,28 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>21</v>
+        <v>461</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>133</v>
+        <v>462</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8838,10 +8952,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8864,13 +8978,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>441</v>
+        <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>442</v>
+        <v>192</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>443</v>
+        <v>193</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8921,7 +9035,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>440</v>
+        <v>194</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8933,7 +9047,7 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -8942,7 +9056,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>444</v>
+        <v>195</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8953,21 +9067,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -8979,15 +9093,17 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>446</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>447</v>
+        <v>197</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9036,19 +9152,19 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>445</v>
+        <v>200</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
@@ -9057,7 +9173,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>449</v>
+        <v>195</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9068,42 +9184,46 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>446</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9151,19 +9271,19 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
@@ -9172,7 +9292,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>449</v>
+        <v>133</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9183,10 +9303,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9209,20 +9329,18 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9270,7 +9388,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9288,10 +9406,10 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>459</v>
+        <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9302,10 +9420,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9328,17 +9446,15 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>462</v>
+        <v>191</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>463</v>
+        <v>192</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9387,7 +9503,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>461</v>
+        <v>194</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9399,41 +9515,41 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>467</v>
+        <v>195</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>468</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9445,15 +9561,17 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>441</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>470</v>
+        <v>197</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9502,76 +9620,78 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>469</v>
+        <v>200</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>472</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>473</v>
+        <v>195</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>474</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>446</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9619,28 +9739,28 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>480</v>
+        <v>133</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9651,10 +9771,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9677,13 +9797,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9734,7 +9854,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9755,10 +9875,10 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
@@ -9766,10 +9886,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9780,7 +9900,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9792,13 +9912,13 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>420</v>
+        <v>484</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9849,7 +9969,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9867,10 +9987,10 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>489</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9881,10 +10001,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9907,13 +10027,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>193</v>
+        <v>484</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>194</v>
+        <v>489</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>195</v>
+        <v>490</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9964,7 +10084,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>196</v>
+        <v>488</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9976,7 +10096,7 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
@@ -9985,7 +10105,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>197</v>
+        <v>487</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9996,21 +10116,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -10022,18 +10142,20 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>135</v>
+        <v>492</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>199</v>
+        <v>493</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>200</v>
+        <v>494</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10081,28 +10203,28 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>202</v>
+        <v>491</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>21</v>
+        <v>497</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>197</v>
+        <v>498</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10113,46 +10235,44 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>428</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>500</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>429</v>
+        <v>501</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>430</v>
+        <v>502</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -10200,42 +10320,42 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>431</v>
+        <v>499</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>21</v>
+        <v>504</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>133</v>
+        <v>505</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>21</v>
+        <v>506</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10243,7 +10363,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>90</v>
@@ -10258,17 +10378,15 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -10293,13 +10411,13 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>499</v>
+        <v>21</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10317,10 +10435,10 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>90</v>
@@ -10335,24 +10453,24 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>502</v>
+        <v>512</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10375,15 +10493,17 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>183</v>
+        <v>484</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10408,13 +10528,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>506</v>
+        <v>21</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>507</v>
+        <v>21</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10432,7 +10552,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10450,24 +10570,24 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>510</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10481,7 +10601,7 @@
         <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
@@ -10490,13 +10610,13 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10547,7 +10667,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10562,16 +10682,16 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>515</v>
+        <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>508</v>
+        <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>21</v>
@@ -10579,14 +10699,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10605,17 +10725,15 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>519</v>
+        <v>458</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10664,13 +10782,13 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
@@ -10682,10 +10800,10 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>21</v>
+        <v>527</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10696,10 +10814,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10710,7 +10828,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10722,17 +10840,15 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>525</v>
+        <v>191</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>526</v>
+        <v>192</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10781,38 +10897,855 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>524</v>
+        <v>194</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
+      <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK75" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO75" t="s" s="2">
+      <c r="AK78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO75">
+  <autoFilter ref="A1:AO82">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10822,7 +11755,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI81">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -278,7 +278,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}allDosagesSameCategory:Alle Dosierungsanweisungen eines MedicationRequest müssen dieselbe Dosierungskategorie aufweisen. {dosageInstruction.extension.where(url = 'https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category').value.coding.code.distinct().count() = 1}FirstDosageSequenceNumberExists:Wenn mehrere Dosierungsanweisungen vorhanden sind, muss mindestens eine davon die Sequenznummer 1 haben. {dosageInstruction.count() &lt;= 1 or dosageInstruction.sequence.where($this = 1).exists()}e-med-continuous-medication-effectiveDosePeriod:Eine Dauermedikation (courseOfTherapyType = #continuous) darf kein Enddatum besitzen. {courseOfTherapyType.where(coding.code='continuous' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists().not()}e-med-acute-medication-effectiveDosePeriod:Eine Akutmedikation (courseOfTherapyType = #acute) muss ein Enddatum besitzen. {courseOfTherapyType.where(coding.code='acute' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}allDosagesSameCategory:Alle Dosierungsanweisungen eines MedicationRequest müssen dieselbe Dosierungskategorie aufweisen. {dosageInstruction.extension.where(url = 'https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category').value.coding.code.distinct().count() = 1}FirstDosageSequenceNumberExists:Wenn mehrere Dosierungsanweisungen vorhanden sind, muss mindestens eine davon die Sequenznummer 1 haben. {dosageInstruction.count() &lt;= 1 or dosageInstruction.sequence.where($this = 1).exists()}at-emed-planeintrag-status-reason-beim-absetzen:Bei Status 'stopped' oder 'entered-in-error' muss ein statusReason angegeben werden. {(status = 'stopped' or status = 'entered-in-error') implies statusReason.coding.code.exists()}e-med-continuous-medication-effectiveDosePeriod:Eine Dauermedikation (courseOfTherapyType = #continuous) darf kein Enddatum besitzen. {courseOfTherapyType.where(coding.code='continuous' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists().not()}e-med-acute-medication-effectiveDosePeriod:Eine Akutmedikation (courseOfTherapyType = #acute) muss ein Enddatum besitzen. {courseOfTherapyType.where(coding.code='acute' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -871,7 +871,6 @@
   &lt;coding&gt;
     &lt;system value="https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS"/&gt;
     &lt;code value="1"/&gt;
-    &lt;display value="Planeintrag"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$93</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3059" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -867,21 +867,7 @@
     <t>The category can be used to include where the medication is expected to be consumed or other types of requests.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS"/&gt;
-    &lt;code value="1"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedicationRequestCategoryVS</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -894,6 +880,48 @@
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
   </si>
   <si>
+    <t>MedicationRequest.category.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.system</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
     <t>MedicationRequest.priority</t>
   </si>
   <si>
@@ -977,7 +1005,7 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-medikation) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -1170,6 +1198,9 @@
   </si>
   <si>
     <t>If specified without indicating a performer, this indicates that the performer must be of the specified type. If specified with a performer then it indicates the requirements of the performer if the designated performer is not available.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Identifies the type of individual that is desired to administer the medication.</t>
@@ -2132,7 +2163,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO82"/>
+  <dimension ref="A1:AO93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -2159,7 +2190,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="138.53125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="104.39453125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="71.75" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -5390,28 +5421,26 @@
         <v>21</v>
       </c>
       <c r="S28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5447,10 +5476,10 @@
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>267</v>
@@ -5461,10 +5490,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5475,7 +5504,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -5484,16 +5513,16 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>192</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>193</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5520,13 +5549,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5544,7 +5573,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>194</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5556,19 +5585,19 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>284</v>
+        <v>195</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5576,42 +5605,42 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
+        <v>197</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>288</v>
+        <v>198</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>289</v>
+        <v>159</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5649,31 +5678,31 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>200</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
@@ -5682,7 +5711,7 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>195</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5693,10 +5722,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5707,7 +5736,7 @@
         <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5719,16 +5748,20 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5764,23 +5797,25 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>207</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5795,25 +5830,23 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>296</v>
+        <v>208</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5822,7 +5855,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5831,16 +5864,16 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>299</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>192</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
+        <v>193</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5891,7 +5924,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>194</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5903,7 +5936,7 @@
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
@@ -5912,7 +5945,7 @@
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>296</v>
+        <v>195</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -5921,45 +5954,45 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>197</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5996,31 +6029,31 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>200</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -6029,7 +6062,7 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>296</v>
+        <v>195</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
@@ -6038,12 +6071,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6057,7 +6090,7 @@
         <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -6066,18 +6099,20 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>305</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>213</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>214</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -6086,7 +6121,7 @@
         <v>21</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -6125,10 +6160,10 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>217</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -6140,27 +6175,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>311</v>
+        <v>218</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>312</v>
+        <v>21</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>313</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6168,13 +6203,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -6183,16 +6218,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>315</v>
+        <v>191</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>221</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>222</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>318</v>
+        <v>223</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6242,10 +6277,10 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>224</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>90</v>
@@ -6257,27 +6292,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>321</v>
+        <v>225</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>323</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6285,10 +6320,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -6297,21 +6332,21 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>228</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -6320,7 +6355,7 @@
         <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>21</v>
@@ -6359,7 +6394,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>231</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6374,27 +6409,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>329</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>330</v>
+        <v>232</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>332</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>285</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6405,7 +6440,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -6414,19 +6449,21 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>334</v>
+        <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>335</v>
+        <v>235</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>336</v>
+        <v>236</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6474,13 +6511,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6489,27 +6526,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>338</v>
+        <v>239</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6517,13 +6554,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6532,16 +6569,20 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>340</v>
+        <v>242</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>243</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6589,7 +6630,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>247</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6604,27 +6645,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>248</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>249</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>287</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>287</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6632,13 +6673,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6647,16 +6688,20 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>349</v>
+        <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>350</v>
+        <v>288</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6704,7 +6749,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>348</v>
+        <v>255</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6719,27 +6764,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>321</v>
+        <v>256</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>289</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>354</v>
+        <v>289</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6759,16 +6804,16 @@
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>355</v>
+        <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>357</v>
+        <v>291</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6795,13 +6840,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>21</v>
+        <v>293</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6819,7 +6864,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>354</v>
+        <v>289</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6834,16 +6879,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>358</v>
+        <v>294</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>359</v>
+        <v>295</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>360</v>
+        <v>296</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6851,10 +6896,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6871,22 +6916,22 @@
         <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>362</v>
+        <v>298</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>363</v>
+        <v>299</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>364</v>
+        <v>300</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6912,13 +6957,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>365</v>
+        <v>21</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6936,7 +6981,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6951,13 +6996,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>368</v>
+        <v>301</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6968,10 +7013,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>302</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>302</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6979,10 +7024,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6991,16 +7036,16 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>370</v>
+        <v>242</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>372</v>
+        <v>304</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7039,19 +7084,17 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>302</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7072,10 +7115,10 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>373</v>
+        <v>307</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -7083,12 +7126,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>21</v>
       </c>
@@ -7106,20 +7151,18 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>183</v>
+        <v>310</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>376</v>
+        <v>311</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7144,13 +7187,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -7168,13 +7211,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>302</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -7183,29 +7226,31 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>381</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>307</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
@@ -7214,29 +7259,27 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>387</v>
+        <v>242</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7285,13 +7328,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>302</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -7300,27 +7343,27 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>307</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>315</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>315</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7328,13 +7371,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -7343,15 +7386,17 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>394</v>
+        <v>316</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>395</v>
+        <v>317</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7400,13 +7445,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>315</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -7415,27 +7460,27 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>397</v>
+        <v>320</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>398</v>
+        <v>322</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>21</v>
+        <v>324</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7443,13 +7488,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7458,15 +7503,17 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>104</v>
+        <v>326</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>400</v>
+        <v>327</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7515,13 +7562,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7530,27 +7577,27 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>21</v>
+        <v>331</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>398</v>
+        <v>332</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>335</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7570,18 +7617,20 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>403</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>404</v>
+        <v>337</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7630,13 +7679,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>402</v>
+        <v>335</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7645,27 +7694,27 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>407</v>
+        <v>341</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>408</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>408</v>
+        <v>344</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7685,21 +7734,19 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>163</v>
+        <v>345</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>409</v>
+        <v>346</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>410</v>
+        <v>347</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>411</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7747,13 +7794,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>408</v>
+        <v>344</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7762,16 +7809,16 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>412</v>
+        <v>348</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>413</v>
+        <v>349</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7779,10 +7826,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>350</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>350</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7802,20 +7849,18 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>415</v>
+        <v>352</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7840,13 +7885,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>419</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7864,7 +7909,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>414</v>
+        <v>350</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7879,27 +7924,27 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>21</v>
+        <v>355</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>420</v>
+        <v>356</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>421</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>421</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7907,28 +7952,28 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>422</v>
+        <v>360</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>361</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>423</v>
+        <v>362</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7979,13 +8024,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>421</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -7994,27 +8039,27 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>424</v>
+        <v>363</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>425</v>
+        <v>332</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>365</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>365</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8025,10 +8070,10 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -8037,13 +8082,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>427</v>
+        <v>366</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>428</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>429</v>
+        <v>368</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8094,13 +8139,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>426</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8109,16 +8154,16 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>430</v>
+        <v>369</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>431</v>
+        <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>432</v>
+        <v>370</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>21</v>
+        <v>371</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8126,10 +8171,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8137,31 +8182,31 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>434</v>
+        <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>435</v>
+        <v>373</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>436</v>
+        <v>374</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>437</v>
+        <v>375</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8187,35 +8232,37 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AC52" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>433</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -8224,13 +8271,13 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8239,16 +8286,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8257,10 +8302,10 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -8269,17 +8314,15 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>443</v>
+        <v>382</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>444</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8328,13 +8371,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>433</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -8343,31 +8386,29 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>440</v>
+        <v>385</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>445</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8376,10 +8417,10 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -8388,16 +8429,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>447</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>389</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
+        <v>390</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8423,13 +8464,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8447,7 +8488,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8462,31 +8503,29 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>439</v>
+        <v>393</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>395</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>398</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8495,10 +8534,10 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8507,16 +8546,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>444</v>
+        <v>400</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>401</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8566,7 +8605,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8581,31 +8620,29 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>404</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>405</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8614,29 +8651,27 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K56" t="s" s="2">
-        <v>453</v>
+        <v>406</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8685,7 +8720,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8700,13 +8735,13 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8715,16 +8750,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>454</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8733,29 +8766,27 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K57" t="s" s="2">
-        <v>456</v>
+        <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8804,7 +8835,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8819,13 +8850,13 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8836,10 +8867,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8859,16 +8890,16 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>458</v>
+        <v>415</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>459</v>
+        <v>416</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>460</v>
+        <v>417</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8919,13 +8950,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -8934,13 +8965,13 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>461</v>
+        <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>462</v>
+        <v>419</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8951,10 +8982,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>463</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>463</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8965,7 +8996,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -8974,19 +9005,21 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>192</v>
+        <v>421</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>193</v>
+        <v>422</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9034,7 +9067,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>194</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9046,16 +9079,16 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>195</v>
+        <v>425</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -9064,26 +9097,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>464</v>
+        <v>426</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>464</v>
+        <v>426</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -9092,16 +9125,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>197</v>
+        <v>427</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>198</v>
+        <v>428</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>159</v>
+        <v>429</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9127,13 +9160,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9151,19 +9184,19 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>200</v>
+        <v>426</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
@@ -9172,7 +9205,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>195</v>
+        <v>432</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9183,46 +9216,42 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>434</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9270,7 +9299,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9282,16 +9311,16 @@
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>21</v>
+        <v>436</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>133</v>
+        <v>437</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9300,12 +9329,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9316,10 +9345,10 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
@@ -9328,17 +9357,15 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9387,13 +9414,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -9402,13 +9429,13 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>474</v>
+        <v>444</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9419,10 +9446,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9430,13 +9457,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
@@ -9445,15 +9472,17 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>191</v>
+        <v>446</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>192</v>
+        <v>447</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9490,40 +9519,38 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>194</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>21</v>
+        <v>451</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>195</v>
+        <v>452</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9532,16 +9559,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9551,7 +9580,7 @@
         <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
@@ -9560,16 +9589,16 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>455</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>197</v>
+        <v>456</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>198</v>
+        <v>448</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>159</v>
+        <v>449</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9619,7 +9648,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>200</v>
+        <v>445</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9631,16 +9660,16 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>21</v>
+        <v>451</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>195</v>
+        <v>452</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9649,16 +9678,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="D65" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9668,29 +9699,27 @@
         <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>459</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9738,7 +9767,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9750,16 +9779,16 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>21</v>
+        <v>451</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>133</v>
+        <v>452</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9768,14 +9797,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9784,10 +9815,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9796,15 +9827,17 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9853,13 +9886,13 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>478</v>
+        <v>445</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
@@ -9868,13 +9901,13 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>21</v>
+        <v>451</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9883,14 +9916,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9899,10 +9934,10 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
@@ -9911,15 +9946,17 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9968,13 +10005,13 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>483</v>
+        <v>445</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -9983,13 +10020,13 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>21</v>
+        <v>451</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>487</v>
+        <v>452</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9998,14 +10035,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10014,10 +10053,10 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
@@ -10026,15 +10065,17 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10083,13 +10124,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>488</v>
+        <v>445</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -10098,13 +10139,13 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>21</v>
+        <v>451</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>487</v>
+        <v>452</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10115,10 +10156,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10129,7 +10170,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -10141,20 +10182,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10202,7 +10239,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10220,10 +10257,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>498</v>
+        <v>474</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10234,10 +10271,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10260,17 +10297,15 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>500</v>
+        <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>501</v>
+        <v>192</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10319,7 +10354,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>499</v>
+        <v>194</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10331,41 +10366,41 @@
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>504</v>
+        <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>505</v>
+        <v>195</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>506</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -10377,15 +10412,17 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>479</v>
+        <v>135</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>508</v>
+        <v>197</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -10434,76 +10471,78 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>507</v>
+        <v>200</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>510</v>
+        <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>511</v>
+        <v>195</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>512</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>477</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>477</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>478</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>484</v>
+        <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>479</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
+        <v>480</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10551,28 +10590,28 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>513</v>
+        <v>481</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>518</v>
+        <v>133</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10583,10 +10622,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10609,15 +10648,17 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>520</v>
+        <v>470</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>521</v>
+        <v>483</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10666,7 +10707,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>519</v>
+        <v>482</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10687,10 +10728,10 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>21</v>
@@ -10698,10 +10739,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10712,7 +10753,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -10724,13 +10765,13 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>458</v>
+        <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>525</v>
+        <v>192</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>526</v>
+        <v>193</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10781,7 +10822,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>524</v>
+        <v>194</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10793,16 +10834,16 @@
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>527</v>
+        <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>528</v>
+        <v>195</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10813,21 +10854,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>488</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -10839,15 +10880,17 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10896,19 +10939,19 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
@@ -10928,14 +10971,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>530</v>
+        <v>489</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>530</v>
+        <v>489</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>156</v>
+        <v>478</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10948,24 +10991,26 @@
         <v>21</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>197</v>
+        <v>479</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>198</v>
+        <v>480</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="O76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11013,7 +11058,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>200</v>
+        <v>481</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11034,7 +11079,7 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>195</v>
+        <v>133</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11045,46 +11090,42 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>531</v>
+        <v>490</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>531</v>
+        <v>490</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>135</v>
+        <v>491</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11132,19 +11173,19 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
@@ -11153,7 +11194,7 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>133</v>
+        <v>494</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11164,10 +11205,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>532</v>
+        <v>495</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>532</v>
+        <v>495</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11175,7 +11216,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>90</v>
@@ -11190,17 +11231,15 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>533</v>
+        <v>496</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>536</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -11225,13 +11264,13 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>537</v>
+        <v>21</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>538</v>
+        <v>21</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -11249,10 +11288,10 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>532</v>
+        <v>495</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>90</v>
@@ -11267,24 +11306,24 @@
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>527</v>
+        <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>539</v>
+        <v>499</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>540</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>541</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>541</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11307,13 +11346,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>183</v>
+        <v>496</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>542</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11340,13 +11379,13 @@
         <v>21</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>544</v>
+        <v>21</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>545</v>
+        <v>21</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>21</v>
@@ -11364,7 +11403,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>541</v>
+        <v>500</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11382,24 +11421,24 @@
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>546</v>
+        <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>547</v>
+        <v>499</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>548</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>549</v>
+        <v>503</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>549</v>
+        <v>503</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11413,7 +11452,7 @@
         <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>21</v>
@@ -11422,16 +11461,20 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>550</v>
+        <v>504</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>551</v>
+        <v>505</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
@@ -11479,7 +11522,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>549</v>
+        <v>503</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11494,13 +11537,13 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>553</v>
+        <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>554</v>
+        <v>510</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11511,21 +11554,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>556</v>
+        <v>21</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
@@ -11537,16 +11580,16 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>557</v>
+        <v>512</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>558</v>
+        <v>513</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>559</v>
+        <v>514</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>560</v>
+        <v>515</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11596,13 +11639,13 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
@@ -11614,24 +11657,24 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>561</v>
+        <v>517</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>21</v>
+        <v>518</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11642,7 +11685,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
@@ -11654,17 +11697,15 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>563</v>
+        <v>491</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>564</v>
+        <v>520</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>566</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11713,13 +11754,13 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
@@ -11728,23 +11769,1302 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AL82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM82" t="s" s="2">
+      <c r="B92" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AN82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO82" t="s" s="2">
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO82">
+  <autoFilter ref="A1:AO93">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11754,7 +13074,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI81">
+  <conditionalFormatting sqref="A2:AI92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
   </si>
   <si>
     <t>Ein Planeintrag im Medikationsplan wird durch eine "MedicationRequest"-Ressource abgebildet.
-Sie enthält genau ein Arzneimittel mit dessen Dosierung, wobei das Arzneimittel verpflichtend mit einer contained Medication-Ressource dokumentiert wird.
+Sie enthält genau ein Arzneimittel mit dessen Dosierung, wobei das Arzneimittel entweder verpflichtend mit einer contained Medication-Ressource oder einer logischen Referenz über die PZN dokumentiert wird.
 Der Planeintrag kann in weiterer Folge als Grundlage für die Erstellung einer "Geplanten Abgabe" dienen. Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
@@ -495,7 +495,7 @@
 </t>
   </si>
   <si>
-    <t>Vollständige Darstellung der Dosierungsanweisungen</t>
+    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definiert Regeln befüllt.</t>
   </si>
   <si>
     <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>
@@ -800,7 +800,7 @@
     <t>MedicationRequest.statusReason.text</t>
   </si>
   <si>
-    <t>Begründung für den Status des Planeintrags (Freitext), z.B. warum ein Medikament abgesetzt wurde.</t>
+    <t>Begründung falls der Code 'other' angegeben wurde (Freitext).</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1009,7 +1009,7 @@
 </t>
   </si>
   <si>
-    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als logische Referenz dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -1046,7 +1046,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den der Planeintrag ausgestellt werden soll, der über den Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
+    <t>ELGA-Teilnehmer, für den der Medikationsplan dokumentiert wird.</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -1237,7 +1237,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Grund für die Verordnung des Arzneimittels. Entweder Code oder Referenz. Verwendung erst, wenn codierte Angabe möglich.</t>
+    <t>Reason or indication for ordering or not ordering the medication</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1274,7 +1274,7 @@
 </t>
   </si>
   <si>
-    <t>Condition or observation that supports why the prescription is being written</t>
+    <t>Grund für die Verordnung des Arzneimittels. Wird zu einem späteren Zeitpunkt im Kontext von EDiagnose ergänzt.</t>
   </si>
   <si>
     <t>Condition or observation that supports why the medication was ordered.</t>
@@ -9345,7 +9345,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>91</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="583">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1492,6 +1492,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+frequencySameAsWhenCount:wenn .when verwendet wird und periodUnit = d muss die frequency mit der Anzahl an entries in .when übereinstimmen {(timing.repeat.when.exists() and timing.repeat.periodUnit = 'd') implies timing.repeat.when.distinct().count() = timing.repeat.frequency}weekdaysRequireWeeklyPeriod:DayOfWeek kann nur dann verwendet werden, wenn periodUnit 'wk' ist. {timing.repeat.dayOfWeek.exists() implies timing.repeat.periodUnit = 'wk'}frequencyEqualsEventWeekdayProduct:Wenn Wochentage angegeben sind dann entspricht die frequency dem Produkt aus Wochentagen und der Anzahl an ausgewählten Tageszeiten. {timing.repeat.when.exists() and timing.repeat.dayOfWeek.exists() implies timing.repeat.frequency = timing.repeat.when.distinct().count() * timing.repeat.dayOfWeek.distinct().count()}noDuplicateWhen:Tageszeiten können nicht mehrmals vorkommen. {timing.repeat.when.count() = timing.repeat.when.distinct().count()}noDuplicateDayOfWeek:Wochentage können nicht mehrmals vorkommen. {timing.repeat.dayOfWeek.count() = timing.repeat.dayOfWeek.distinct().count()}allowedPeriodUnitsForStandardAdministration:Für Standarddosierungen im Tageszeitenschema sind nur tägliche, wöchentliche oder monatliche Wiederholungen zulässig. {timing.repeat.periodUnit = 'd' or timing.repeat.periodUnit = 'wk' or timing.repeat.periodUnit = 'm'}</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest</t>
   </si>
   <si>
@@ -1569,6 +1573,10 @@
   </si>
   <si>
     <t>The amount or quantity to provide as part of the first dispense.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>Supply.quantity[moodCode=RQO]</t>
@@ -10136,7 +10144,7 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>469</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>451</v>
@@ -10156,10 +10164,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10182,13 +10190,13 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10239,7 +10247,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10257,10 +10265,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10271,10 +10279,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10386,10 +10394,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10503,14 +10511,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10532,10 +10540,10 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>159</v>
@@ -10590,7 +10598,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10622,10 +10630,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10648,16 +10656,16 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10707,7 +10715,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10728,7 +10736,7 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10739,10 +10747,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10854,10 +10862,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10971,14 +10979,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11000,10 +11008,10 @@
         <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>159</v>
@@ -11058,7 +11066,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11090,10 +11098,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11116,13 +11124,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11173,7 +11181,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11185,7 +11193,7 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>495</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
@@ -11194,7 +11202,7 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11205,10 +11213,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11231,13 +11239,13 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11288,7 +11296,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11309,7 +11317,7 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11320,10 +11328,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11346,13 +11354,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11403,7 +11411,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11424,7 +11432,7 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -11435,10 +11443,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11461,19 +11469,19 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -11522,7 +11530,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11540,10 +11548,10 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11554,10 +11562,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11580,16 +11588,16 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11639,7 +11647,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11657,24 +11665,24 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11697,13 +11705,13 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11754,7 +11762,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11766,30 +11774,30 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>495</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11812,16 +11820,16 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11871,7 +11879,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -11889,10 +11897,10 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -11903,10 +11911,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11929,13 +11937,13 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11986,7 +11994,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12007,7 +12015,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>386</v>
@@ -12018,10 +12026,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12044,13 +12052,13 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12101,7 +12109,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12119,10 +12127,10 @@
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12133,10 +12141,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12248,10 +12256,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12365,14 +12373,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12394,10 +12402,10 @@
         <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>159</v>
@@ -12452,7 +12460,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12484,10 +12492,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12510,16 +12518,16 @@
         <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12548,10 +12556,10 @@
         <v>376</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -12569,7 +12577,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>90</v>
@@ -12587,24 +12595,24 @@
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12630,10 +12638,10 @@
         <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12663,10 +12671,10 @@
         <v>376</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -12684,7 +12692,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12702,24 +12710,24 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12742,13 +12750,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12799,7 +12807,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12814,13 +12822,13 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
@@ -12831,14 +12839,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12857,16 +12865,16 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12916,7 +12924,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -12937,7 +12945,7 @@
         <v>21</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>21</v>
@@ -12948,10 +12956,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12974,16 +12982,16 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13033,7 +13041,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13048,13 +13056,13 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$105</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3908" uniqueCount="637">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -303,7 +303,7 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
+    <t>Technische id der Ressource</t>
   </si>
   <si>
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
@@ -335,14 +335,191 @@
 </t>
   </si>
   <si>
-    <t>MedicationRequest.implicitRules</t>
+    <t>MedicationRequest.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>MedicationRequest.implicitRules</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -408,6 +585,59 @@
     <t>Act.text?</t>
   </si>
   <si>
+    <t>MedicationRequest.text.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.status</t>
+  </si>
+  <si>
+    <t>generated | extensions | additional | empty</t>
+  </si>
+  <si>
+    <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of a resource narrative.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/narrative-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Narrative.status</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.div</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xhtml
+</t>
+  </si>
+  <si>
+    <t>Limited xhtml content</t>
+  </si>
+  <si>
+    <t>The actual narrative content, a stripped down version of XHTML.</t>
+  </si>
+  <si>
+    <t>The contents of the html element are an XHTML fragment containing only the basic html formatting elements described in chapters 7-11 and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained stylesheets. The XHTML content SHALL NOT contain a head, a body, external stylesheet references, scripts, forms, base/link/xlink, frames, iframes and objects.</t>
+  </si>
+  <si>
+    <t>Narrative.div</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+txt-1:The narrative SHALL contain only the basic html formatting elements and attributes described in chapters 7-11 (except section 4 of chapter 9) and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained style attributes {htmlChecks()}txt-2:The narrative SHALL have some non-whitespace content {htmlChecks()}</t>
+  </si>
+  <si>
     <t>MedicationRequest.contained</t>
   </si>
   <si>
@@ -431,34 +661,16 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>MedicationRequest.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationRequest.extension:effectiveDosePeriod</t>
@@ -508,10 +720,6 @@
     <t>MedicationRequest.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -519,9 +727,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -571,9 +776,6 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/PlaneintragStatusVS</t>
   </si>
   <si>
@@ -617,42 +819,10 @@
     <t>MedicationRequest.statusReason.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationRequest.statusReason.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>MedicationRequest.statusReason.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Codierte Begründung für den Status des Planeintrags.</t>
@@ -1198,9 +1368,6 @@
   </si>
   <si>
     <t>If specified without indicating a performer, this indicates that the performer must be of the specified type. If specified with a performer then it indicates the requirements of the performer if the designated performer is not available.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Identifies the type of individual that is desired to administer the medication.</t>
@@ -2171,7 +2338,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO93"/>
+  <dimension ref="A1:AO105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -2456,7 +2623,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2475,7 +2642,7 @@
         <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>21</v>
@@ -2573,7 +2740,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2592,7 +2759,7 @@
         <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -2710,10 +2877,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>104</v>
@@ -2724,9 +2891,7 @@
       <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2775,7 +2940,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2787,7 +2952,7 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -2796,7 +2961,7 @@
         <v>21</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>21</v>
@@ -2814,14 +2979,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2833,16 +2998,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2868,43 +3033,43 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
@@ -2913,7 +3078,7 @@
         <v>21</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>21</v>
@@ -2922,16 +3087,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2941,16 +3106,16 @@
         <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>121</v>
@@ -3030,53 +3195,53 @@
         <v>21</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="AN7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" hidden="true">
-      <c r="A8" t="s" s="2">
-        <v>126</v>
-      </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3126,19 +3291,19 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
@@ -3147,7 +3312,7 @@
         <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>21</v>
@@ -3158,10 +3323,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3169,11 +3334,11 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
       </c>
@@ -3181,18 +3346,20 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -3229,29 +3396,31 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
@@ -3269,46 +3438,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3358,7 +3525,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3367,10 +3534,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -3390,14 +3557,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -3406,7 +3571,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3415,19 +3580,19 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3453,13 +3618,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -3477,7 +3642,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3486,10 +3651,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3509,14 +3674,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3529,26 +3694,24 @@
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J12" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3572,13 +3735,13 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -3596,7 +3759,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3608,7 +3771,7 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3617,7 +3780,7 @@
         <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>21</v>
@@ -3628,10 +3791,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3642,28 +3805,28 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3713,13 +3876,13 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
@@ -3728,27 +3891,27 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3756,31 +3919,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3806,11 +3969,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3828,10 +3993,10 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>90</v>
@@ -3843,16 +4008,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
@@ -3860,14 +4025,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3886,16 +4051,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3921,11 +4086,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3943,7 +4110,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3958,13 +4125,13 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>21</v>
@@ -3975,10 +4142,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4001,13 +4168,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4058,7 +4225,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>107</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4079,7 +4246,7 @@
         <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>21</v>
@@ -4090,14 +4257,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4116,16 +4283,16 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>113</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4163,19 +4330,19 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>199</v>
+        <v>116</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4187,7 +4354,7 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
@@ -4196,7 +4363,7 @@
         <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
@@ -4205,12 +4372,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4218,35 +4385,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -4270,13 +4433,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -4294,13 +4457,13 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
@@ -4315,21 +4478,21 @@
         <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4337,13 +4500,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -4352,15 +4515,17 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4409,10 +4574,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>90</v>
@@ -4421,7 +4586,7 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
@@ -4430,7 +4595,7 @@
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>21</v>
@@ -4441,14 +4606,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4467,16 +4632,16 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4514,19 +4679,19 @@
         <v>21</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4538,7 +4703,7 @@
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
@@ -4547,7 +4712,7 @@
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4558,10 +4723,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4569,10 +4734,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4581,23 +4746,19 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -4633,31 +4794,29 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
@@ -4666,29 +4825,31 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
@@ -4700,19 +4861,19 @@
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4762,19 +4923,19 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
@@ -4783,29 +4944,31 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
@@ -4817,21 +4980,21 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4879,19 +5042,19 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
@@ -4900,54 +5063,56 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4996,19 +5161,19 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
@@ -5017,21 +5182,21 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>240</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5051,23 +5216,21 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -5115,13 +5278,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -5130,27 +5293,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5158,7 +5321,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -5167,26 +5330,24 @@
         <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -5210,13 +5371,11 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -5234,10 +5393,10 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -5249,27 +5408,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5277,7 +5436,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
@@ -5286,22 +5445,22 @@
         <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>110</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5312,7 +5471,7 @@
         <v>21</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>21</v>
@@ -5327,13 +5486,11 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5351,10 +5508,10 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>90</v>
@@ -5366,27 +5523,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5394,13 +5551,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -5409,17 +5566,15 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>105</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5444,11 +5599,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5466,31 +5623,31 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>107</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>108</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>21</v>
@@ -5498,21 +5655,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -5524,15 +5681,17 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5569,31 +5728,31 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>194</v>
+        <v>118</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
@@ -5602,7 +5761,7 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5613,14 +5772,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5636,21 +5795,23 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5686,19 +5847,19 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>200</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5710,7 +5871,7 @@
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
@@ -5719,21 +5880,21 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5741,11 +5902,11 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G31" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5753,23 +5914,19 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>202</v>
+        <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>278</v>
+        <v>105</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5817,19 +5974,19 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
@@ -5838,32 +5995,32 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5875,15 +6032,17 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5920,31 +6079,31 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>118</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
@@ -5953,7 +6112,7 @@
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -5964,21 +6123,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5987,21 +6146,23 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>197</v>
+        <v>268</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>198</v>
+        <v>269</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -6037,31 +6198,31 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -6070,21 +6231,21 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>195</v>
+        <v>273</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6092,7 +6253,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -6110,17 +6271,15 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>213</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>214</v>
+        <v>277</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -6129,7 +6288,7 @@
         <v>21</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>21</v>
@@ -6168,7 +6327,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6189,21 +6348,21 @@
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>219</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6211,7 +6370,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>90</v>
@@ -6226,18 +6385,18 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>221</v>
+        <v>283</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -6285,7 +6444,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6306,21 +6465,21 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>225</v>
+        <v>287</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>226</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6328,7 +6487,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
@@ -6343,17 +6502,17 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>229</v>
+        <v>291</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>230</v>
+        <v>292</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6363,7 +6522,7 @@
         <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>21</v>
@@ -6402,7 +6561,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>231</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6423,21 +6582,21 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>232</v>
+        <v>294</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>233</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6460,17 +6619,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>235</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6519,7 +6680,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6540,21 +6701,21 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>240</v>
+        <v>304</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6568,7 +6729,7 @@
         <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6577,19 +6738,19 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>244</v>
+        <v>307</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>246</v>
+        <v>309</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6638,7 +6799,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6659,21 +6820,21 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>248</v>
+        <v>311</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>249</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6681,35 +6842,33 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>252</v>
+        <v>315</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6718,7 +6877,7 @@
         <v>21</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>21</v>
@@ -6733,13 +6892,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6757,10 +6916,10 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>255</v>
+        <v>313</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>90</v>
@@ -6772,27 +6931,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>320</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>256</v>
+        <v>321</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6800,30 +6959,32 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>110</v>
+        <v>248</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6848,13 +7009,11 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6872,13 +7031,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6887,16 +7046,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>294</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6904,10 +7063,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6918,29 +7077,27 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>298</v>
+        <v>105</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6989,7 +7146,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>297</v>
+        <v>107</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7001,7 +7158,7 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -7010,7 +7167,7 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>301</v>
+        <v>108</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -7021,21 +7178,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -7044,18 +7201,20 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>242</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -7092,29 +7251,31 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>306</v>
+        <v>117</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>302</v>
+        <v>118</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
@@ -7123,7 +7284,7 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>307</v>
+        <v>108</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -7134,23 +7295,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -7162,16 +7321,20 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>310</v>
+        <v>144</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -7219,13 +7382,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -7240,25 +7403,23 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
@@ -7270,22 +7431,22 @@
         <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>242</v>
+        <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>304</v>
+        <v>106</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7336,7 +7497,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7348,7 +7509,7 @@
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -7357,7 +7518,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>307</v>
+        <v>108</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7366,44 +7527,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>316</v>
+        <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>317</v>
+        <v>112</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>318</v>
+        <v>113</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>319</v>
+        <v>114</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7441,54 +7602,54 @@
         <v>21</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>118</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>322</v>
+        <v>108</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7502,7 +7663,7 @@
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7511,18 +7672,20 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>326</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>328</v>
+        <v>269</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7531,7 +7694,7 @@
         <v>21</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>21</v>
@@ -7570,10 +7733,10 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>325</v>
+        <v>272</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>90</v>
@@ -7585,27 +7748,27 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>332</v>
+        <v>273</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>334</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7616,7 +7779,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7625,19 +7788,19 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>336</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>337</v>
+        <v>276</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>338</v>
+        <v>277</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7687,7 +7850,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7702,27 +7865,27 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>343</v>
+        <v>281</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7730,10 +7893,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7742,19 +7905,21 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>345</v>
+        <v>166</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>346</v>
+        <v>283</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7763,7 +7928,7 @@
         <v>21</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>21</v>
@@ -7802,13 +7967,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>344</v>
+        <v>286</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7817,27 +7982,27 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7845,13 +8010,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7860,16 +8025,18 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>351</v>
+        <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>353</v>
+        <v>291</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7917,7 +8084,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>350</v>
+        <v>293</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7932,27 +8099,27 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>355</v>
+        <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>356</v>
+        <v>294</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>358</v>
+        <v>295</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7960,13 +8127,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7975,16 +8142,20 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>360</v>
+        <v>297</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>361</v>
+        <v>298</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -8032,7 +8203,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8047,27 +8218,27 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8078,7 +8249,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -8087,19 +8258,23 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>366</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -8147,7 +8322,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>365</v>
+        <v>310</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8162,27 +8337,27 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>21</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8205,17 +8380,15 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8240,13 +8413,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>376</v>
+        <v>187</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8264,7 +8437,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8279,16 +8452,16 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8296,10 +8469,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8316,21 +8489,23 @@
         <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>382</v>
+        <v>297</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8379,7 +8554,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8400,10 +8575,10 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>385</v>
+        <v>356</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8411,10 +8586,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8422,10 +8597,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -8434,20 +8609,18 @@
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>183</v>
+        <v>297</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8472,37 +8645,35 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
@@ -8511,29 +8682,31 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>393</v>
+        <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>396</v>
+        <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8551,20 +8724,18 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8613,13 +8784,13 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>357</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
@@ -8628,29 +8799,31 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>403</v>
+        <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>404</v>
+        <v>362</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>396</v>
+        <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8659,10 +8832,10 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -8671,13 +8844,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>406</v>
+        <v>297</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8728,13 +8901,13 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>357</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
@@ -8743,13 +8916,13 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>410</v>
+        <v>362</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8758,12 +8931,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8771,13 +8944,13 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8786,15 +8959,17 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>104</v>
+        <v>371</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8843,13 +9018,13 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
@@ -8858,27 +9033,27 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8886,13 +9061,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
@@ -8901,15 +9076,17 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8958,13 +9135,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -8973,27 +9150,27 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>21</v>
+        <v>389</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9013,21 +9190,21 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>163</v>
+        <v>391</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9075,7 +9252,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9090,27 +9267,27 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>424</v>
+        <v>395</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>425</v>
+        <v>396</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>21</v>
+        <v>398</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9118,13 +9295,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -9133,17 +9310,15 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>183</v>
+        <v>400</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9168,13 +9343,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>431</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9192,13 +9367,13 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
@@ -9207,27 +9382,27 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9235,28 +9410,28 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9307,13 +9482,13 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
@@ -9322,27 +9497,27 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9350,7 +9525,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>90</v>
@@ -9362,16 +9537,16 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9422,13 +9597,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -9437,16 +9612,16 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>444</v>
+        <v>387</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
@@ -9454,10 +9629,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9465,13 +9640,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
@@ -9480,17 +9655,15 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9527,23 +9700,25 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
@@ -9552,31 +9727,29 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9585,28 +9758,28 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K64" t="s" s="2">
-        <v>455</v>
+        <v>248</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>428</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9632,13 +9805,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9656,13 +9829,13 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
@@ -9671,13 +9844,13 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9686,16 +9859,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9704,10 +9875,10 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>
@@ -9716,17 +9887,15 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9775,13 +9944,13 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
@@ -9790,31 +9959,29 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>451</v>
+        <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9823,10 +9990,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9835,16 +10002,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>462</v>
+        <v>248</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9870,13 +10037,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9894,7 +10061,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9909,31 +10076,29 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM66" t="s" s="2">
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AN66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="B67" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9942,10 +10107,10 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
@@ -9954,16 +10119,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10013,7 +10178,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10028,31 +10193,29 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10061,29 +10224,27 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K68" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10132,7 +10293,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10144,16 +10305,16 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>469</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10164,10 +10325,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10187,16 +10348,16 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>471</v>
+        <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10247,13 +10408,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -10265,10 +10426,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>474</v>
+        <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10279,10 +10440,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10293,7 +10454,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -10302,16 +10463,16 @@
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>191</v>
+        <v>469</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>192</v>
+        <v>470</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>193</v>
+        <v>471</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10362,28 +10523,28 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>194</v>
+        <v>468</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>21</v>
+        <v>472</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>195</v>
+        <v>473</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -10394,21 +10555,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -10417,21 +10578,21 @@
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>135</v>
+        <v>229</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>197</v>
+        <v>475</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10479,28 +10640,28 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>200</v>
+        <v>474</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>21</v>
+        <v>478</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>195</v>
+        <v>479</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -10509,48 +10670,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10574,13 +10733,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>21</v>
+        <v>484</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>21</v>
+        <v>485</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10598,19 +10757,19 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
@@ -10619,7 +10778,7 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>133</v>
+        <v>486</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10630,10 +10789,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10644,7 +10803,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -10656,17 +10815,15 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10715,13 +10872,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -10730,13 +10887,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>21</v>
+        <v>490</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10745,12 +10902,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10764,7 +10921,7 @@
         <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
@@ -10773,13 +10930,13 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>191</v>
+        <v>493</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>192</v>
+        <v>494</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>193</v>
+        <v>495</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10830,28 +10987,28 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>194</v>
+        <v>492</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>21</v>
+        <v>496</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>21</v>
+        <v>497</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>195</v>
+        <v>498</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10862,24 +11019,24 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>21</v>
@@ -10888,16 +11045,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>500</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>197</v>
+        <v>501</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>198</v>
+        <v>502</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>159</v>
+        <v>503</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10935,19 +11092,17 @@
         <v>21</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>200</v>
+        <v>499</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10959,16 +11114,16 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>21</v>
+        <v>505</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>195</v>
+        <v>506</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10977,16 +11132,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="D76" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10996,29 +11153,27 @@
         <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>135</v>
+        <v>509</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11066,7 +11221,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11078,16 +11233,16 @@
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>21</v>
+        <v>505</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>133</v>
+        <v>506</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11096,14 +11251,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11112,10 +11269,10 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>21</v>
@@ -11124,15 +11281,17 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -11181,28 +11340,28 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>495</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>21</v>
+        <v>505</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11211,14 +11370,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>21</v>
       </c>
@@ -11227,10 +11388,10 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>21</v>
@@ -11239,15 +11400,17 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -11296,13 +11459,13 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
@@ -11311,13 +11474,13 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>21</v>
+        <v>505</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11326,14 +11489,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>21</v>
       </c>
@@ -11342,10 +11507,10 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
@@ -11354,15 +11519,17 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11411,13 +11578,13 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
@@ -11426,13 +11593,13 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>21</v>
+        <v>505</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -11441,14 +11608,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C80" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="D80" t="s" s="2">
         <v>21</v>
       </c>
@@ -11457,10 +11626,10 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>21</v>
@@ -11469,20 +11638,18 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
@@ -11530,28 +11697,28 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AK80" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AL80" t="s" s="2">
-        <v>511</v>
+        <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11562,10 +11729,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11576,7 +11743,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
@@ -11588,17 +11755,15 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11647,7 +11812,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11665,24 +11830,24 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>520</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11705,13 +11870,13 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>492</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>522</v>
+        <v>105</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>523</v>
+        <v>106</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11762,7 +11927,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>521</v>
+        <v>107</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11774,41 +11939,41 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>495</v>
+        <v>21</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>524</v>
+        <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>525</v>
+        <v>108</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>526</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -11820,16 +11985,16 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>498</v>
+        <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>528</v>
+        <v>112</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>529</v>
+        <v>113</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>530</v>
+        <v>114</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11879,28 +12044,28 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>527</v>
+        <v>118</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>531</v>
+        <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>532</v>
+        <v>108</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -11911,42 +12076,46 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>21</v>
+        <v>533</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+      <c r="N84" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11994,19 +12163,19 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>21</v>
@@ -12015,10 +12184,10 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>537</v>
+        <v>191</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>21</v>
@@ -12026,10 +12195,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12040,7 +12209,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>21</v>
@@ -12052,15 +12221,17 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>471</v>
+        <v>525</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12109,7 +12280,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12127,10 +12298,10 @@
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12141,10 +12312,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12167,13 +12338,13 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12224,7 +12395,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>194</v>
+        <v>107</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12245,7 +12416,7 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
@@ -12256,14 +12427,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12282,16 +12453,16 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>198</v>
+        <v>113</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12341,7 +12512,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12353,7 +12524,7 @@
         <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>21</v>
@@ -12362,7 +12533,7 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
@@ -12373,14 +12544,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>479</v>
+        <v>533</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12399,19 +12570,19 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>480</v>
+        <v>534</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>481</v>
+        <v>535</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>160</v>
+        <v>226</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -12460,7 +12631,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12472,7 +12643,7 @@
         <v>21</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>21</v>
@@ -12481,7 +12652,7 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
@@ -12492,10 +12663,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12503,7 +12674,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>90</v>
@@ -12518,17 +12689,15 @@
         <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>550</v>
-      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -12553,13 +12722,13 @@
         <v>21</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>551</v>
+        <v>21</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>552</v>
+        <v>21</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -12577,10 +12746,10 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>90</v>
@@ -12589,30 +12758,30 @@
         <v>21</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>102</v>
+        <v>549</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>541</v>
+        <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>554</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12635,13 +12804,13 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>183</v>
+        <v>552</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12668,13 +12837,13 @@
         <v>21</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>558</v>
+        <v>21</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>559</v>
+        <v>21</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -12692,7 +12861,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12710,24 +12879,24 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>560</v>
+        <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>562</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12741,7 +12910,7 @@
         <v>90</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
@@ -12750,13 +12919,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12807,7 +12976,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12822,13 +12991,13 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>567</v>
+        <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>560</v>
+        <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
@@ -12839,21 +13008,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>570</v>
+        <v>21</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>21</v>
@@ -12865,18 +13034,20 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>21</v>
       </c>
@@ -12924,13 +13095,13 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>21</v>
@@ -12942,10 +13113,10 @@
         <v>21</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>21</v>
+        <v>565</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>21</v>
@@ -12956,10 +13127,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12970,7 +13141,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>21</v>
@@ -12982,16 +13153,16 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13041,13 +13212,13 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>21</v>
@@ -13056,23 +13227,1417 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AL93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM93" t="s" s="2">
+      <c r="B95" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO93" t="s" s="2">
+      <c r="M95" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO93">
+  <autoFilter ref="A1:AO105">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13082,7 +14647,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI92">
+  <conditionalFormatting sqref="A2:AI104">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$117</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3908" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4344" uniqueCount="682">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -697,6 +697,129 @@
 </t>
   </si>
   <si>
+    <t>MedicationRequest.extension:effectiveDosePeriod.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:effectiveDosePeriod.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:effectiveDosePeriod.url</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:effectiveDosePeriod.value[x]</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Period over which the medication is to be taken</t>
+  </si>
+  <si>
+    <t>The period over which the medication is to be taken.  Where there are multiple dosageInstruction lines (for example, tapering doses), this is the earliest date and the latest end date of the dosageInstructions.</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:effectiveDosePeriod.value[x].id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:effectiveDosePeriod.value[x].extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:effectiveDosePeriod.value[x].start</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.value[x].start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:effectiveDosePeriod.value[x].end</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension.value[x].end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>./high</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
     <t>MedicationRequest.extension:renderedDosageInstruction</t>
   </si>
   <si>
@@ -717,17 +840,35 @@
 Element `MedicationRequest.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
+    <t>MedicationRequest.extension:renderedDosageInstruction.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:renderedDosageInstruction.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:renderedDosageInstruction.url</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:renderedDosageInstruction.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
+    <t>Full representation of the dosage instructions</t>
+  </si>
+  <si>
+    <t>The full representation of the dose of the medication included in all dosage instructions.  To be used when multiple dosage instructions are included to represent complex dosing such as increasing or tapering doses.</t>
+  </si>
+  <si>
     <t>MedicationRequest.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -740,7 +881,7 @@
 </t>
   </si>
   <si>
-    <t>Planeintrag-ID.</t>
+    <t>External ids for this request</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -1292,10 +1433,6 @@
     <t>MedicationRequest.authoredOn</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
     <t>Datum der Erstellung des Planeintrags.</t>
   </si>
   <si>
@@ -1702,6 +1839,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
@@ -1775,10 +1915,6 @@
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.validityPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>Time period supply is authorized for</t>
@@ -2338,10 +2474,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO105"/>
+  <dimension ref="A1:AO117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.57421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3451,10 +3587,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>91</v>
@@ -4834,7 +4970,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>210</v>
       </c>
@@ -4855,7 +4991,7 @@
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
@@ -4958,11 +5094,9 @@
         <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C23" t="s" s="2">
         <v>218</v>
       </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4983,17 +5117,15 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>220</v>
+        <v>105</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -5042,19 +5174,19 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
@@ -5063,7 +5195,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -5074,27 +5206,27 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>21</v>
@@ -5103,17 +5235,13 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -5149,19 +5277,19 @@
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>118</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5182,7 +5310,7 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
@@ -5193,10 +5321,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5204,7 +5332,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
@@ -5219,16 +5347,16 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>229</v>
+        <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5236,7 +5364,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -5278,42 +5406,42 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>235</v>
+        <v>191</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5321,7 +5449,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -5330,23 +5458,21 @@
         <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -5371,11 +5497,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -5393,10 +5521,10 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -5408,27 +5536,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5442,7 +5570,7 @@
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -5451,17 +5579,15 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5486,11 +5612,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5508,7 +5636,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5520,16 +5648,16 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>254</v>
+        <v>108</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
@@ -5540,21 +5668,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -5566,15 +5694,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5611,31 +5741,31 @@
         <v>21</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
@@ -5653,44 +5783,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>111</v>
+        <v>240</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>112</v>
+        <v>241</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>113</v>
+        <v>242</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5728,31 +5858,31 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>118</v>
+        <v>244</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
@@ -5761,21 +5891,21 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>108</v>
+        <v>246</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5786,10 +5916,10 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -5798,24 +5928,24 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>144</v>
+        <v>240</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q30" s="2"/>
+      <c r="Q30" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="R30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5859,16 +5989,16 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5880,23 +6010,25 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5908,7 +6040,7 @@
         <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5917,15 +6049,17 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>259</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>105</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5974,19 +6108,19 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
@@ -5995,7 +6129,7 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -6006,21 +6140,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -6032,17 +6166,15 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -6079,31 +6211,31 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
@@ -6123,10 +6255,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>267</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6137,7 +6269,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -6146,23 +6278,19 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>268</v>
+        <v>207</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -6198,31 +6326,31 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>118</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
@@ -6231,21 +6359,21 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6253,7 +6381,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -6265,19 +6393,19 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6285,7 +6413,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -6327,10 +6455,10 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>227</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -6339,7 +6467,7 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
@@ -6348,21 +6476,21 @@
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>229</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6370,33 +6498,31 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>285</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -6444,7 +6570,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6465,21 +6591,21 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>287</v>
+        <v>191</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>288</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6490,30 +6616,28 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>291</v>
+        <v>208</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -6561,19 +6685,19 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>21</v>
@@ -6582,21 +6706,21 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>294</v>
+        <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>295</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6607,7 +6731,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -6616,23 +6740,21 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6680,13 +6802,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6695,27 +6817,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>304</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6723,7 +6845,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
@@ -6732,26 +6854,24 @@
         <v>91</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6775,13 +6895,11 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6799,10 +6917,10 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>90</v>
@@ -6814,27 +6932,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>312</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6842,7 +6960,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
@@ -6851,22 +6969,22 @@
         <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>166</v>
+        <v>294</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6877,7 +6995,7 @@
         <v>21</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>317</v>
+        <v>21</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>21</v>
@@ -6894,11 +7012,9 @@
       <c r="X39" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y39" t="s" s="2">
-        <v>318</v>
-      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6916,10 +7032,10 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>90</v>
@@ -6931,27 +7047,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6959,13 +7075,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6974,17 +7090,15 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>248</v>
+        <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>324</v>
+        <v>105</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -7009,11 +7123,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -7031,31 +7147,31 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>323</v>
+        <v>107</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>329</v>
+        <v>108</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -7063,21 +7179,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -7089,15 +7205,17 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -7134,31 +7252,31 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -7178,14 +7296,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7201,21 +7319,23 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>112</v>
+        <v>304</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>113</v>
+        <v>305</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -7251,19 +7371,19 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>118</v>
+        <v>308</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7275,7 +7395,7 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
@@ -7284,21 +7404,21 @@
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>108</v>
+        <v>309</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7306,10 +7426,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -7318,23 +7438,19 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>333</v>
+        <v>105</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -7382,19 +7498,19 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>262</v>
+        <v>107</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
@@ -7403,32 +7519,32 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>263</v>
+        <v>108</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -7440,15 +7556,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7485,31 +7603,31 @@
         <v>21</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -7529,21 +7647,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -7552,21 +7670,23 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>112</v>
+        <v>314</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>113</v>
+        <v>315</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7602,31 +7722,31 @@
         <v>21</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>118</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
@@ -7635,21 +7755,21 @@
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>108</v>
+        <v>319</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>21</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7657,7 +7777,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
@@ -7672,20 +7792,18 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>268</v>
+        <v>322</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7694,7 +7812,7 @@
         <v>21</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>21</v>
@@ -7733,7 +7851,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>272</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7754,21 +7872,21 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>273</v>
+        <v>326</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>274</v>
+        <v>327</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7776,7 +7894,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>90</v>
@@ -7791,18 +7909,18 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7850,7 +7968,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7871,21 +7989,21 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>281</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7893,7 +8011,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7908,17 +8026,17 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>283</v>
+        <v>336</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7928,7 +8046,7 @@
         <v>21</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>21</v>
@@ -7967,7 +8085,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7988,21 +8106,21 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>287</v>
+        <v>340</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>288</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8025,17 +8143,19 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>104</v>
+        <v>343</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>290</v>
+        <v>344</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>292</v>
+        <v>347</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -8084,7 +8204,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8105,21 +8225,21 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>295</v>
+        <v>350</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8133,7 +8253,7 @@
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -8142,19 +8262,19 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>297</v>
+        <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>298</v>
+        <v>352</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>299</v>
+        <v>353</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -8203,7 +8323,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8224,21 +8344,21 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>303</v>
+        <v>357</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>304</v>
+        <v>358</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8246,35 +8366,33 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>307</v>
+        <v>361</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -8283,7 +8401,7 @@
         <v>21</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>21</v>
@@ -8298,13 +8416,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -8322,10 +8440,10 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>310</v>
+        <v>359</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>90</v>
@@ -8337,27 +8455,27 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>312</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8365,30 +8483,32 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>166</v>
+        <v>294</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8415,11 +8535,9 @@
       <c r="X52" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>347</v>
-      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8437,13 +8555,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -8452,16 +8570,16 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8469,10 +8587,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8483,29 +8601,27 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>297</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>353</v>
+        <v>105</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8554,7 +8670,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>352</v>
+        <v>107</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8566,7 +8682,7 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -8575,7 +8691,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>356</v>
+        <v>108</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8586,21 +8702,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -8609,18 +8725,20 @@
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>358</v>
+        <v>112</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8657,29 +8775,31 @@
         <v>21</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AC54" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="AD54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>361</v>
+        <v>117</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>357</v>
+        <v>118</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
@@ -8688,7 +8808,7 @@
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>362</v>
+        <v>108</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8699,23 +8819,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -8727,16 +8845,20 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>365</v>
+        <v>144</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8784,13 +8906,13 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
@@ -8805,25 +8927,23 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>362</v>
+        <v>309</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8835,22 +8955,22 @@
         <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>297</v>
+        <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>369</v>
+        <v>105</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>359</v>
+        <v>106</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8901,7 +9021,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>357</v>
+        <v>107</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8913,7 +9033,7 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -8922,7 +9042,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>362</v>
+        <v>108</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8931,44 +9051,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>371</v>
+        <v>111</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>372</v>
+        <v>112</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>373</v>
+        <v>113</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>374</v>
+        <v>114</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9006,54 +9126,54 @@
         <v>21</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>370</v>
+        <v>118</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>377</v>
+        <v>108</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9067,7 +9187,7 @@
         <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
@@ -9076,18 +9196,20 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>381</v>
+        <v>132</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>382</v>
+        <v>314</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>383</v>
+        <v>315</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9096,7 +9218,7 @@
         <v>21</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>21</v>
@@ -9135,10 +9257,10 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>318</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>90</v>
@@ -9150,27 +9272,27 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>387</v>
+        <v>319</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>388</v>
+        <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>389</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9181,7 +9303,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9190,19 +9312,19 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>391</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>392</v>
+        <v>322</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>393</v>
+        <v>323</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>394</v>
+        <v>324</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9252,7 +9374,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>390</v>
+        <v>325</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9267,27 +9389,27 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>396</v>
+        <v>326</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>398</v>
+        <v>327</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9295,10 +9417,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -9307,19 +9429,21 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>400</v>
+        <v>166</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9328,7 +9452,7 @@
         <v>21</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>21</v>
@@ -9367,13 +9491,13 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>399</v>
+        <v>332</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
@@ -9382,27 +9506,27 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>403</v>
+        <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>404</v>
+        <v>333</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9410,13 +9534,13 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>21</v>
@@ -9425,16 +9549,18 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>406</v>
+        <v>104</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>407</v>
+        <v>336</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>408</v>
+        <v>337</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9482,7 +9608,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>405</v>
+        <v>339</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9497,27 +9623,27 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>412</v>
+        <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>413</v>
+        <v>341</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9525,13 +9651,13 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
@@ -9540,16 +9666,20 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>415</v>
+        <v>343</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>416</v>
+        <v>344</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9597,7 +9727,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>414</v>
+        <v>348</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9612,27 +9742,27 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>387</v>
+        <v>349</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>419</v>
+        <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9643,7 +9773,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -9652,19 +9782,23 @@
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>421</v>
+        <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9712,7 +9846,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>420</v>
+        <v>356</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9727,27 +9861,27 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9770,17 +9904,15 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>428</v>
+        <v>391</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9805,13 +9937,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>431</v>
+        <v>393</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>432</v>
+        <v>394</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9829,7 +9961,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9844,16 +9976,16 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>433</v>
+        <v>395</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>434</v>
+        <v>396</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
@@ -9861,10 +9993,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>435</v>
+        <v>398</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>435</v>
+        <v>398</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9881,21 +10013,23 @@
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>436</v>
+        <v>343</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>437</v>
+        <v>399</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9944,7 +10078,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>435</v>
+        <v>398</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9965,10 +10099,10 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>440</v>
+        <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
@@ -9976,10 +10110,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>441</v>
+        <v>403</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>441</v>
+        <v>403</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9987,10 +10121,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9999,20 +10133,18 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>248</v>
+        <v>343</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>442</v>
+        <v>404</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -10037,37 +10169,35 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>445</v>
+        <v>21</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>441</v>
+        <v>403</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
@@ -10076,29 +10206,31 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>447</v>
+        <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>449</v>
+        <v>408</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>450</v>
+        <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>451</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>409</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10116,20 +10248,18 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>454</v>
+        <v>412</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -10178,13 +10308,13 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>452</v>
+        <v>403</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -10193,29 +10323,31 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>457</v>
+        <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>458</v>
+        <v>408</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>450</v>
+        <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>459</v>
+        <v>413</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10224,10 +10356,10 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
@@ -10236,13 +10368,13 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>460</v>
+        <v>343</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>462</v>
+        <v>405</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10293,13 +10425,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>459</v>
+        <v>403</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -10308,13 +10440,13 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>463</v>
+        <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>464</v>
+        <v>408</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10323,12 +10455,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>465</v>
+        <v>416</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>465</v>
+        <v>416</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10336,13 +10468,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>21</v>
@@ -10351,15 +10483,17 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>417</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>466</v>
+        <v>418</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10408,13 +10542,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>465</v>
+        <v>416</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -10423,27 +10557,27 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>21</v>
+        <v>421</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>464</v>
+        <v>423</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>21</v>
+        <v>425</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10451,13 +10585,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
@@ -10466,15 +10600,17 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>469</v>
+        <v>427</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>470</v>
+        <v>428</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10523,13 +10659,13 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
@@ -10538,27 +10674,27 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>472</v>
+        <v>431</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>473</v>
+        <v>433</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>21</v>
+        <v>435</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>436</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>474</v>
+        <v>436</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10578,21 +10714,21 @@
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>229</v>
+        <v>437</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10640,7 +10776,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>474</v>
+        <v>436</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10655,27 +10791,27 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>21</v>
+        <v>444</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10683,13 +10819,13 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
@@ -10698,17 +10834,15 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>248</v>
+        <v>446</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10733,13 +10867,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>484</v>
+        <v>21</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10757,13 +10891,13 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
@@ -10772,27 +10906,27 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>486</v>
+        <v>450</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>487</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>487</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10800,28 +10934,28 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>488</v>
+        <v>240</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10872,13 +11006,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>487</v>
+        <v>451</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -10887,27 +11021,27 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>491</v>
+        <v>456</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>21</v>
+        <v>458</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10915,7 +11049,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>90</v>
@@ -10927,16 +11061,16 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>493</v>
+        <v>460</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10987,13 +11121,13 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
@@ -11002,16 +11136,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>497</v>
+        <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>498</v>
+        <v>433</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>21</v>
+        <v>464</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>21</v>
@@ -11019,10 +11153,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>499</v>
+        <v>465</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>499</v>
+        <v>465</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11030,13 +11164,13 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>21</v>
@@ -11045,17 +11179,15 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>500</v>
+        <v>466</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -11092,23 +11224,25 @@
         <v>21</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>361</v>
+        <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>499</v>
+        <v>465</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
@@ -11117,31 +11251,29 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>505</v>
+        <v>469</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11150,28 +11282,28 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K76" t="s" s="2">
-        <v>509</v>
+        <v>294</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11197,13 +11329,13 @@
         <v>21</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>21</v>
+        <v>476</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>21</v>
+        <v>477</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -11221,13 +11353,13 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
@@ -11236,13 +11368,13 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11251,16 +11383,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11269,10 +11399,10 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>21</v>
@@ -11281,17 +11411,15 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>513</v>
+        <v>481</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -11340,13 +11468,13 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
@@ -11355,31 +11483,29 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>505</v>
+        <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>21</v>
+        <v>485</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>514</v>
+        <v>486</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>21</v>
       </c>
@@ -11388,10 +11514,10 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>21</v>
@@ -11400,16 +11526,16 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>516</v>
+        <v>294</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11435,13 +11561,13 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>21</v>
+        <v>490</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>21</v>
+        <v>491</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -11459,7 +11585,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11474,31 +11600,29 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>21</v>
+        <v>495</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>21</v>
+        <v>496</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>21</v>
       </c>
@@ -11507,10 +11631,10 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
@@ -11519,16 +11643,16 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11578,7 +11702,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11593,31 +11717,29 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>21</v>
+        <v>495</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>21</v>
       </c>
@@ -11626,29 +11748,27 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K80" t="s" s="2">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -11697,7 +11817,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11709,16 +11829,16 @@
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>523</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11729,10 +11849,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11752,16 +11872,16 @@
         <v>21</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>525</v>
+        <v>132</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11812,13 +11932,13 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
@@ -11830,10 +11950,10 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>528</v>
+        <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -11844,10 +11964,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11858,7 +11978,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
@@ -11867,16 +11987,16 @@
         <v>21</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>104</v>
+        <v>514</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>105</v>
+        <v>515</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>106</v>
+        <v>516</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11927,28 +12047,28 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>107</v>
+        <v>513</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>21</v>
+        <v>517</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>108</v>
+        <v>518</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -11959,21 +12079,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -11982,21 +12102,21 @@
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>275</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>112</v>
+        <v>520</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
       </c>
@@ -12044,28 +12164,28 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>118</v>
+        <v>519</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>21</v>
+        <v>523</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>108</v>
+        <v>524</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12074,48 +12194,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>533</v>
+        <v>21</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>111</v>
+        <v>294</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -12139,13 +12257,13 @@
         <v>21</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>21</v>
+        <v>529</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>21</v>
+        <v>530</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>21</v>
@@ -12163,19 +12281,19 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>21</v>
@@ -12184,7 +12302,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>191</v>
+        <v>531</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12195,10 +12313,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12209,7 +12327,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>21</v>
@@ -12221,17 +12339,15 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12280,13 +12396,13 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>21</v>
@@ -12295,13 +12411,13 @@
         <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>21</v>
+        <v>535</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12310,12 +12426,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12329,7 +12445,7 @@
         <v>90</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>21</v>
@@ -12338,13 +12454,13 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>104</v>
+        <v>538</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>105</v>
+        <v>539</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>106</v>
+        <v>540</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12395,28 +12511,28 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>107</v>
+        <v>537</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>21</v>
+        <v>541</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>21</v>
+        <v>542</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>108</v>
+        <v>543</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
@@ -12427,24 +12543,24 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>21</v>
@@ -12453,16 +12569,16 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>111</v>
+        <v>545</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>112</v>
+        <v>546</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>113</v>
+        <v>547</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>114</v>
+        <v>548</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12500,19 +12616,17 @@
         <v>21</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>118</v>
+        <v>544</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12524,16 +12638,16 @@
         <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>21</v>
+        <v>550</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>108</v>
+        <v>551</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
@@ -12542,16 +12656,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="C88" s="2"/>
+      <c r="C88" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="D88" t="s" s="2">
-        <v>533</v>
+        <v>21</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12561,29 +12677,27 @@
         <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>111</v>
+        <v>554</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
@@ -12631,7 +12745,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12643,16 +12757,16 @@
         <v>21</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>21</v>
+        <v>550</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>191</v>
+        <v>551</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
@@ -12661,14 +12775,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="D89" t="s" s="2">
         <v>21</v>
       </c>
@@ -12677,10 +12793,10 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
@@ -12689,15 +12805,17 @@
         <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -12746,28 +12864,28 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>549</v>
+        <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>21</v>
+        <v>550</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
@@ -12776,14 +12894,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="D90" t="s" s="2">
         <v>21</v>
       </c>
@@ -12792,10 +12912,10 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
@@ -12804,15 +12924,17 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -12861,13 +12983,13 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>21</v>
@@ -12876,13 +12998,13 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>21</v>
+        <v>550</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
@@ -12891,14 +13013,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>21</v>
       </c>
@@ -12907,10 +13031,10 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>21</v>
@@ -12919,15 +13043,17 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -12976,13 +13102,13 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>21</v>
@@ -12991,13 +13117,13 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>21</v>
+        <v>550</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
@@ -13006,14 +13132,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="D92" t="s" s="2">
         <v>21</v>
       </c>
@@ -13022,10 +13150,10 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>21</v>
@@ -13034,20 +13162,18 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>21</v>
       </c>
@@ -13095,28 +13221,28 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>102</v>
+        <v>568</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>21</v>
+        <v>550</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>565</v>
+        <v>21</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>21</v>
@@ -13127,10 +13253,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13141,7 +13267,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>21</v>
@@ -13153,17 +13279,15 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -13212,7 +13336,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13230,16 +13354,16 @@
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>574</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" hidden="true">
@@ -13270,13 +13394,13 @@
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>546</v>
+        <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>576</v>
+        <v>105</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>577</v>
+        <v>106</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13327,7 +13451,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>575</v>
+        <v>107</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13339,41 +13463,41 @@
         <v>21</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>549</v>
+        <v>21</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>578</v>
+        <v>21</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>579</v>
+        <v>108</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>580</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>21</v>
@@ -13385,16 +13509,16 @@
         <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>552</v>
+        <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>582</v>
+        <v>112</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>583</v>
+        <v>113</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>584</v>
+        <v>114</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13444,28 +13568,28 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>581</v>
+        <v>118</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>585</v>
+        <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>586</v>
+        <v>108</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>21</v>
@@ -13476,42 +13600,46 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>21</v>
+        <v>578</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>588</v>
+        <v>111</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
       </c>
@@ -13559,19 +13687,19 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>21</v>
@@ -13580,10 +13708,10 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>591</v>
+        <v>191</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>440</v>
+        <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>21</v>
@@ -13591,10 +13719,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13605,7 +13733,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>21</v>
@@ -13617,15 +13745,17 @@
         <v>21</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>525</v>
+        <v>570</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -13674,7 +13804,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13692,10 +13822,10 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>595</v>
+        <v>21</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
@@ -13706,10 +13836,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13821,10 +13951,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13938,14 +14068,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>533</v>
+        <v>578</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -13967,16 +14097,16 @@
         <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>534</v>
+        <v>579</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>535</v>
+        <v>580</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>226</v>
+        <v>581</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -14025,7 +14155,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>536</v>
+        <v>582</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14057,10 +14187,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14068,7 +14198,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>90</v>
@@ -14083,17 +14213,15 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>604</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14118,13 +14246,13 @@
         <v>21</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>605</v>
+        <v>21</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>606</v>
+        <v>21</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>21</v>
@@ -14142,10 +14270,10 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>90</v>
@@ -14154,30 +14282,30 @@
         <v>21</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>102</v>
+        <v>595</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>595</v>
+        <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>608</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14200,13 +14328,13 @@
         <v>21</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>248</v>
+        <v>598</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14233,13 +14361,13 @@
         <v>21</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>612</v>
+        <v>21</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>613</v>
+        <v>21</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14257,7 +14385,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14275,24 +14403,24 @@
         <v>21</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>614</v>
+        <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>616</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14306,7 +14434,7 @@
         <v>90</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>21</v>
@@ -14315,13 +14443,13 @@
         <v>21</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>618</v>
+        <v>598</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14372,7 +14500,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14387,13 +14515,13 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>621</v>
+        <v>21</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>614</v>
+        <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
@@ -14404,21 +14532,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>624</v>
+        <v>21</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>21</v>
@@ -14430,18 +14558,20 @@
         <v>21</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>625</v>
+        <v>230</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
       </c>
@@ -14489,13 +14619,13 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>21</v>
@@ -14507,10 +14637,10 @@
         <v>21</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>21</v>
+        <v>610</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
@@ -14521,10 +14651,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14535,7 +14665,7 @@
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>21</v>
@@ -14547,16 +14677,16 @@
         <v>21</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>631</v>
+        <v>613</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>632</v>
+        <v>614</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>633</v>
+        <v>615</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14606,13 +14736,13 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>21</v>
@@ -14621,23 +14751,1417 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AL105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM105" t="s" s="2">
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="AN105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO105" t="s" s="2">
+      <c r="AN108" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO117" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO105">
+  <autoFilter ref="A1:AO117">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14647,7 +16171,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI104">
+  <conditionalFormatting sqref="A2:AI116">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5636" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5636" uniqueCount="789">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1238,7 +1238,7 @@
     <t>MedicationRequest.category.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
+    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>MedicationRequest.priority</t>
@@ -1483,9 +1483,6 @@
   </si>
   <si>
     <t>MedicationRequest.subject.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
     <t>The purpose of this identifier.</t>
@@ -7644,7 +7641,7 @@
         <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>91</v>
@@ -9167,7 +9164,7 @@
         <v>90</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>91</v>
@@ -10107,7 +10104,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -12437,7 +12434,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -12452,16 +12449,16 @@
         <v>166</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -12489,28 +12486,28 @@
         <v>187</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="Z83" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12531,7 +12528,7 @@
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12542,10 +12539,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12571,16 +12568,16 @@
         <v>295</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -12608,28 +12605,28 @@
         <v>148</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12650,21 +12647,21 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12690,16 +12687,16 @@
         <v>132</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12712,43 +12709,43 @@
         <v>21</v>
       </c>
       <c r="T85" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12769,21 +12766,21 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>492</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12809,13 +12806,13 @@
         <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12829,43 +12826,43 @@
         <v>21</v>
       </c>
       <c r="T86" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12886,21 +12883,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12926,10 +12923,10 @@
         <v>231</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12980,7 +12977,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13001,21 +12998,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>506</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13038,16 +13035,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13097,7 +13094,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13118,21 +13115,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>514</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13246,10 +13243,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13272,16 +13269,16 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13331,7 +13328,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13346,27 +13343,27 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13389,13 +13386,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13446,7 +13443,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13461,16 +13458,16 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="AL91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>530</v>
-      </c>
       <c r="AN91" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>21</v>
@@ -13478,10 +13475,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13507,10 +13504,10 @@
         <v>241</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13561,7 +13558,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13576,27 +13573,27 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL92" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="AL92" t="s" s="2">
+      <c r="AM92" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>538</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13619,13 +13616,13 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13676,7 +13673,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13691,7 +13688,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
@@ -13700,7 +13697,7 @@
         <v>456</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>21</v>
@@ -13708,10 +13705,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13734,13 +13731,13 @@
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13791,7 +13788,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13806,16 +13803,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AL94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>21</v>
@@ -13823,10 +13820,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13852,13 +13849,13 @@
         <v>295</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13887,11 +13884,11 @@
         <v>156</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>557</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>21</v>
       </c>
@@ -13908,7 +13905,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13923,13 +13920,13 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>21</v>
@@ -13940,10 +13937,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13966,13 +13963,13 @@
         <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14023,7 +14020,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14044,10 +14041,10 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>21</v>
@@ -14055,10 +14052,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14084,13 +14081,13 @@
         <v>295</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14119,11 +14116,11 @@
         <v>156</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="Z97" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>571</v>
-      </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
       </c>
@@ -14140,7 +14137,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14155,27 +14152,27 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AL97" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AL97" t="s" s="2">
+      <c r="AM97" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AN97" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>576</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14198,16 +14195,16 @@
         <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14257,7 +14254,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14272,16 +14269,16 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>21</v>
@@ -14289,10 +14286,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14315,13 +14312,13 @@
         <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14372,7 +14369,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14387,13 +14384,13 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
@@ -14404,10 +14401,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14433,10 +14430,10 @@
         <v>132</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14487,7 +14484,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14508,7 +14505,7 @@
         <v>21</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>
@@ -14519,10 +14516,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14545,13 +14542,13 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14602,7 +14599,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14617,13 +14614,13 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>21</v>
@@ -14634,10 +14631,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14663,14 +14660,14 @@
         <v>276</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14719,7 +14716,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14734,13 +14731,13 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
@@ -14751,10 +14748,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14780,13 +14777,13 @@
         <v>295</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14816,7 +14813,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -14834,7 +14831,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14855,7 +14852,7 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
@@ -14866,10 +14863,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14981,10 +14978,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15098,10 +15095,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15112,7 +15109,7 @@
         <v>90</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>91</v>
@@ -15217,10 +15214,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15332,10 +15329,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15449,10 +15446,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15568,10 +15565,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15685,10 +15682,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15802,10 +15799,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15919,10 +15916,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16038,10 +16035,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16052,7 +16049,7 @@
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>21</v>
@@ -16157,10 +16154,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16183,13 +16180,13 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16240,7 +16237,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16255,13 +16252,13 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM115" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16272,10 +16269,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16298,13 +16295,13 @@
         <v>21</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16355,7 +16352,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16370,13 +16367,13 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AL116" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="AL116" t="s" s="2">
+      <c r="AM116" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -16387,10 +16384,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16502,10 +16499,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16619,10 +16616,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16645,16 +16642,16 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16704,7 +16701,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16725,7 +16722,7 @@
         <v>21</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>21</v>
@@ -16736,10 +16733,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16765,10 +16762,10 @@
         <v>241</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16819,7 +16816,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16840,7 +16837,7 @@
         <v>21</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>21</v>
@@ -16851,10 +16848,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16880,10 +16877,10 @@
         <v>269</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16934,7 +16931,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>90</v>
@@ -16955,7 +16952,7 @@
         <v>21</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>21</v>
@@ -16966,10 +16963,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16992,16 +16989,16 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17039,7 +17036,7 @@
         <v>21</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -17049,7 +17046,7 @@
         <v>408</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17064,13 +17061,13 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM122" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>21</v>
@@ -17081,13 +17078,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>21</v>
@@ -17109,16 +17106,16 @@
         <v>21</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17168,7 +17165,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17183,13 +17180,13 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM123" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>21</v>
@@ -17200,13 +17197,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C124" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>21</v>
@@ -17228,16 +17225,16 @@
         <v>21</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17287,7 +17284,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17302,13 +17299,13 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM124" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>21</v>
@@ -17319,13 +17316,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C125" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>21</v>
@@ -17347,16 +17344,16 @@
         <v>21</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17406,7 +17403,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17421,13 +17418,13 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM125" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>21</v>
@@ -17438,13 +17435,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C126" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C126" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>21</v>
@@ -17466,16 +17463,16 @@
         <v>21</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17525,7 +17522,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17540,13 +17537,13 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM126" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>21</v>
@@ -17557,13 +17554,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C127" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C127" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>21</v>
@@ -17585,16 +17582,16 @@
         <v>21</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17644,7 +17641,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17656,16 +17653,16 @@
         <v>21</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AK127" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM127" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>21</v>
@@ -17676,10 +17673,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17702,13 +17699,13 @@
         <v>21</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="M128" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17759,7 +17756,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17777,10 +17774,10 @@
         <v>21</v>
       </c>
       <c r="AL128" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AM128" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>21</v>
@@ -17791,10 +17788,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17906,10 +17903,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18023,14 +18020,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -18052,16 +18049,16 @@
         <v>111</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>21</v>
@@ -18110,7 +18107,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18142,10 +18139,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18168,16 +18165,16 @@
         <v>21</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18227,7 +18224,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18248,7 +18245,7 @@
         <v>21</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>21</v>
@@ -18259,10 +18256,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18374,10 +18371,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18491,14 +18488,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18520,16 +18517,16 @@
         <v>111</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>21</v>
@@ -18578,7 +18575,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18610,10 +18607,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18636,13 +18633,13 @@
         <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18693,7 +18690,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18705,16 +18702,16 @@
         <v>21</v>
       </c>
       <c r="AJ136" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM136" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>21</v>
@@ -18725,10 +18722,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18751,13 +18748,13 @@
         <v>21</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -18808,7 +18805,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18829,7 +18826,7 @@
         <v>21</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
@@ -18840,10 +18837,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18866,13 +18863,13 @@
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -18923,7 +18920,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18944,7 +18941,7 @@
         <v>21</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>21</v>
@@ -18955,10 +18952,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18984,16 +18981,16 @@
         <v>231</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>21</v>
@@ -19042,7 +19039,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19060,10 +19057,10 @@
         <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AM139" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
@@ -19074,10 +19071,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19100,16 +19097,16 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19159,7 +19156,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19177,24 +19174,24 @@
         <v>21</v>
       </c>
       <c r="AL140" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="AM140" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="AM140" t="s" s="2">
+      <c r="AN140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO140" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>728</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19217,13 +19214,13 @@
         <v>21</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19274,7 +19271,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19286,30 +19283,30 @@
         <v>21</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL141" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="AM141" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="AM141" t="s" s="2">
+      <c r="AN141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO141" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>734</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19332,16 +19329,16 @@
         <v>21</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19391,7 +19388,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19409,10 +19406,10 @@
         <v>21</v>
       </c>
       <c r="AL142" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="AM142" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>21</v>
@@ -19423,10 +19420,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19449,13 +19446,13 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19506,7 +19503,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19527,10 +19524,10 @@
         <v>21</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>21</v>
@@ -19538,10 +19535,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19564,13 +19561,13 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19621,7 +19618,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19639,10 +19636,10 @@
         <v>21</v>
       </c>
       <c r="AL144" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="AM144" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>21</v>
@@ -19653,10 +19650,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19768,10 +19765,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19885,14 +19882,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -19914,16 +19911,16 @@
         <v>111</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="N147" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>21</v>
@@ -19972,7 +19969,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20004,10 +20001,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20030,16 +20027,16 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>754</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20068,11 +20065,11 @@
         <v>156</v>
       </c>
       <c r="Y148" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="Z148" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="Z148" t="s" s="2">
-        <v>759</v>
-      </c>
       <c r="AA148" t="s" s="2">
         <v>21</v>
       </c>
@@ -20089,7 +20086,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>90</v>
@@ -20107,24 +20104,24 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AM148" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO148" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>761</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20150,10 +20147,10 @@
         <v>295</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20183,11 +20180,11 @@
         <v>156</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="Z149" t="s" s="2">
         <v>765</v>
       </c>
-      <c r="Z149" t="s" s="2">
-        <v>766</v>
-      </c>
       <c r="AA149" t="s" s="2">
         <v>21</v>
       </c>
@@ -20204,7 +20201,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20222,24 +20219,24 @@
         <v>21</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="AM149" t="s" s="2">
+      <c r="AN149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO149" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>769</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20262,13 +20259,13 @@
         <v>21</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="L150" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="L150" t="s" s="2">
+      <c r="M150" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20319,7 +20316,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20334,13 +20331,13 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AM150" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>21</v>
@@ -20351,14 +20348,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -20377,16 +20374,16 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="L151" t="s" s="2">
+      <c r="M151" t="s" s="2">
         <v>779</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>781</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20436,7 +20433,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20457,7 +20454,7 @@
         <v>21</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
@@ -20468,10 +20465,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20494,16 +20491,16 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>784</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="M152" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20553,7 +20550,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20568,13 +20565,13 @@
         <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM152" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>789</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ein Planeintrag im Medikationsplan wird durch eine "MedicationRequest"-Ressource abgebildet.
-Sie enthält genau ein Arzneimittel mit dessen Dosierung, wobei das Arzneimittel entweder verpflichtend mit einer contained Medication-Ressource oder einer logischen Referenz über die PZN dokumentiert wird.
-Der Planeintrag kann in weiterer Folge als Grundlage für die Erstellung einer "Geplanten Abgabe" dienen. Es werden R5-Backport-Extensions verwendet.</t>
+    <t>Profil für einen Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -916,7 +914,8 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status des Planeintrags. Mögliche Ausprägungen: [active | on-hold | completed | stopped | entered-in-error]. Bedeutung: active: Planeintrag einer aktiven Medikation, die eingenommen werden soll | on-hold: Planeintrag ist pausiert, die Therapie ist unterbrochen (Wiederaufnahme vorgesehen) | completed: Therapie gemäß Planeintrag wie geplant durchgeführt und abgeschlossen | stopped: Therapie gemäß Planeintrag vorzeitig gestoppt und abgeschlossen | entered-in-error: Fehlerhafter Planeintrag storniert und abgeschlossen.</t>
+    <t>Status des Planeintrags. Mögliche Ausprägungen: [active | on-hold | stopped | entered-in-error]. Bedeutung: active: aktuell einzunehmende Medikation | on-hold: pausierte Medikation (aktuell nicht einzunehmen) | stopped: wird nicht weiter verordnet (unabhängig ob vorzeitig abgesetzt, abgeschlossen oder Behandlungszeitraum abgelaufen   
+| entered-in-error: Fehlerhafter Planeintrag storniert und abgeschlossen.</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$163</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5636" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6040" uniqueCount="794">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1430,7 +1430,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-patient)
 </t>
   </si>
   <si>
@@ -1679,7 +1679,7 @@
     <t>MedicationRequest.authoredOn</t>
   </si>
   <si>
-    <t>Datum der Erstellung des Planeintrags.</t>
+    <t>Datum der Verordnung des Planeintrags.</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -1703,11 +1703,11 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
-    <t>GDA welcher den Planeintrag erstellt hat und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
+    <t>GDA welcher den Planeintrag zuletzt bearbeitet hat und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1717,6 +1717,48 @@
   </si>
   <si>
     <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.reference</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.identifier</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.identifier.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.identifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.identifier.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.identifier.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.identifier.system</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.identifier.value</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.identifier.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.identifier.assigner</t>
+  </si>
+  <si>
+    <t>MedicationRequest.requester.display</t>
   </si>
   <si>
     <t>MedicationRequest.performer</t>
@@ -2070,7 +2112,7 @@
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension.value}
+    <t xml:space="preserve">value:extension.value.ofType(CodeableConcept).coding.code}
 </t>
   </si>
   <si>
@@ -2078,36 +2120,6 @@
   </si>
   <si>
     <t>see dosageInstruction mapping</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction:otherDosage</t>
-  </si>
-  <si>
-    <t>otherDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-other-administration}
-</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction:timedDosage</t>
-  </si>
-  <si>
-    <t>timedDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-timed-administration}
-</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction:frequencyDosage</t>
-  </si>
-  <si>
-    <t>frequencyDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-frequency-administration}
-</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction:freitextDosage</t>
@@ -2804,7 +2816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO152"/>
+  <dimension ref="A1:AO163"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.57421875" customWidth="true" bestFit="true"/>
@@ -2817,7 +2829,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="195.8359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="199.48828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2834,7 +2846,7 @@
     <col min="25" max="25" width="104.39453125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="71.75" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="50.23046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -11030,7 +11042,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>90</v>
@@ -13730,13 +13742,13 @@
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>545</v>
+        <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>546</v>
+        <v>105</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>547</v>
+        <v>106</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13787,7 +13799,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>544</v>
+        <v>107</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13799,19 +13811,19 @@
         <v>21</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>548</v>
+        <v>21</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>549</v>
+        <v>108</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>550</v>
+        <v>21</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>21</v>
@@ -13819,21 +13831,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>21</v>
@@ -13842,19 +13854,19 @@
         <v>21</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>295</v>
+        <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>552</v>
+        <v>112</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>553</v>
+        <v>113</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>554</v>
+        <v>114</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13880,52 +13892,52 @@
         <v>21</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>555</v>
+        <v>21</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>556</v>
+        <v>21</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>551</v>
+        <v>118</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>557</v>
+        <v>21</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>558</v>
+        <v>108</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>21</v>
@@ -13934,12 +13946,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13953,24 +13965,26 @@
         <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>560</v>
+        <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>561</v>
+        <v>426</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -14019,7 +14033,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>559</v>
+        <v>429</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14028,7 +14042,7 @@
         <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>102</v>
@@ -14040,10 +14054,10 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>563</v>
+        <v>191</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>564</v>
+        <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>21</v>
@@ -14051,10 +14065,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14065,7 +14079,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>21</v>
@@ -14074,19 +14088,19 @@
         <v>21</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>295</v>
+        <v>132</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>566</v>
+        <v>432</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>567</v>
+        <v>433</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>568</v>
+        <v>434</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14112,13 +14126,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>569</v>
+        <v>435</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>570</v>
+        <v>436</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -14136,13 +14150,13 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>565</v>
+        <v>437</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>21</v>
@@ -14151,27 +14165,27 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>571</v>
+        <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>572</v>
+        <v>21</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>573</v>
+        <v>191</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>574</v>
+        <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>575</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>576</v>
+        <v>548</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>576</v>
+        <v>548</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14182,28 +14196,28 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>577</v>
+        <v>276</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>578</v>
+        <v>439</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>579</v>
+        <v>440</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>580</v>
+        <v>441</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14253,13 +14267,13 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>576</v>
+        <v>442</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>21</v>
@@ -14268,16 +14282,16 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>581</v>
+        <v>21</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>582</v>
+        <v>443</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>574</v>
+        <v>21</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>21</v>
@@ -14285,10 +14299,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>583</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>583</v>
+        <v>549</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14299,7 +14313,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>21</v>
@@ -14308,16 +14322,16 @@
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>584</v>
+        <v>104</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>585</v>
+        <v>105</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>586</v>
+        <v>106</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14368,28 +14382,28 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>583</v>
+        <v>107</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>587</v>
+        <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>588</v>
+        <v>108</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
@@ -14400,14 +14414,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14423,18 +14437,20 @@
         <v>21</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>590</v>
+        <v>112</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>21</v>
@@ -14471,19 +14487,19 @@
         <v>21</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>589</v>
+        <v>118</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14495,7 +14511,7 @@
         <v>21</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>21</v>
@@ -14504,7 +14520,7 @@
         <v>21</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>588</v>
+        <v>108</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>
@@ -14515,10 +14531,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>592</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>592</v>
+        <v>551</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14529,28 +14545,32 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>593</v>
+        <v>166</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>594</v>
+        <v>390</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
       </c>
@@ -14574,13 +14594,13 @@
         <v>21</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>21</v>
+        <v>470</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>21</v>
@@ -14598,13 +14618,13 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>592</v>
+        <v>472</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>21</v>
@@ -14613,27 +14633,27 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>596</v>
+        <v>21</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>597</v>
+        <v>473</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>598</v>
+        <v>552</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>598</v>
+        <v>552</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14644,7 +14664,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>21</v>
@@ -14656,17 +14676,19 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>599</v>
+        <v>475</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>476</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="O102" t="s" s="2">
-        <v>601</v>
+        <v>478</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14691,13 +14713,13 @@
         <v>21</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>21</v>
+        <v>479</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>21</v>
+        <v>480</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14715,7 +14737,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>598</v>
+        <v>481</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14730,27 +14752,27 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>602</v>
+        <v>21</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>603</v>
+        <v>473</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>21</v>
+        <v>482</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>604</v>
+        <v>553</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>604</v>
+        <v>553</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14758,7 +14780,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>90</v>
@@ -14770,21 +14792,23 @@
         <v>21</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>295</v>
+        <v>132</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>605</v>
+        <v>484</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>606</v>
+        <v>485</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="O103" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
       </c>
@@ -14796,7 +14820,7 @@
         <v>21</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>21</v>
+        <v>488</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>21</v>
@@ -14808,11 +14832,13 @@
         <v>21</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y103" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z103" t="s" s="2">
-        <v>608</v>
+        <v>21</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -14830,7 +14856,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>604</v>
+        <v>489</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14851,21 +14877,21 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>609</v>
+        <v>490</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>21</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>610</v>
+        <v>554</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>610</v>
+        <v>554</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14879,24 +14905,26 @@
         <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>105</v>
+        <v>493</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -14909,7 +14937,7 @@
         <v>21</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>21</v>
+        <v>496</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>21</v>
@@ -14945,7 +14973,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>107</v>
+        <v>497</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14957,7 +14985,7 @@
         <v>21</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>21</v>
@@ -14966,32 +14994,32 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>108</v>
+        <v>498</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>21</v>
+        <v>499</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>611</v>
+        <v>555</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>611</v>
+        <v>555</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>21</v>
@@ -15000,20 +15028,18 @@
         <v>21</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>112</v>
+        <v>501</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>21</v>
@@ -15050,31 +15076,31 @@
         <v>21</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>118</v>
+        <v>503</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>21</v>
@@ -15083,21 +15109,21 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>108</v>
+        <v>504</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>21</v>
+        <v>505</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>612</v>
+        <v>556</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>612</v>
+        <v>556</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15105,13 +15131,13 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>21</v>
@@ -15120,20 +15146,18 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>144</v>
+        <v>507</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>380</v>
+        <v>508</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>306</v>
+        <v>509</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>21</v>
       </c>
@@ -15181,13 +15205,13 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>309</v>
+        <v>511</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>21</v>
@@ -15202,21 +15226,21 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>310</v>
+        <v>512</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>311</v>
+        <v>513</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>613</v>
+        <v>557</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>613</v>
+        <v>557</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15236,18 +15260,20 @@
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>105</v>
+        <v>445</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -15296,7 +15322,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>107</v>
+        <v>448</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15308,7 +15334,7 @@
         <v>21</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>21</v>
@@ -15317,7 +15343,7 @@
         <v>21</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>21</v>
@@ -15328,21 +15354,21 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>614</v>
+        <v>558</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>614</v>
+        <v>558</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>21</v>
@@ -15354,17 +15380,15 @@
         <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>111</v>
+        <v>559</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>112</v>
+        <v>560</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>21</v>
@@ -15401,54 +15425,54 @@
         <v>21</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>118</v>
+        <v>558</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>21</v>
+        <v>562</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>108</v>
+        <v>563</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>21</v>
+        <v>564</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>565</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>615</v>
+        <v>565</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15456,13 +15480,13 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>21</v>
@@ -15471,20 +15495,18 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>132</v>
+        <v>295</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>315</v>
+        <v>566</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>316</v>
+        <v>567</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>21</v>
       </c>
@@ -15508,13 +15530,13 @@
         <v>21</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>21</v>
+        <v>569</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>21</v>
+        <v>570</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>21</v>
@@ -15532,7 +15554,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>319</v>
+        <v>565</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15547,27 +15569,27 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>21</v>
+        <v>571</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>320</v>
+        <v>572</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>616</v>
+        <v>573</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>616</v>
+        <v>573</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15581,26 +15603,24 @@
         <v>90</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>104</v>
+        <v>574</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>323</v>
+        <v>575</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>21</v>
@@ -15649,7 +15669,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>326</v>
+        <v>573</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15670,21 +15690,21 @@
         <v>21</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>327</v>
+        <v>577</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>21</v>
+        <v>578</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>617</v>
+        <v>579</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>617</v>
+        <v>579</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15692,33 +15712,33 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>166</v>
+        <v>295</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>21</v>
       </c>
@@ -15742,13 +15762,13 @@
         <v>21</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>21</v>
+        <v>583</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>21</v>
+        <v>584</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>21</v>
@@ -15766,13 +15786,13 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>333</v>
+        <v>579</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>21</v>
@@ -15781,27 +15801,27 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>21</v>
+        <v>585</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>21</v>
+        <v>586</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>334</v>
+        <v>587</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>21</v>
+        <v>588</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>335</v>
+        <v>589</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15812,30 +15832,30 @@
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>104</v>
+        <v>591</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>337</v>
+        <v>592</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>21</v>
       </c>
@@ -15883,13 +15903,13 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>340</v>
+        <v>590</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>21</v>
@@ -15898,27 +15918,27 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>21</v>
+        <v>595</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>341</v>
+        <v>596</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>21</v>
+        <v>588</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>619</v>
+        <v>597</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>619</v>
+        <v>597</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15929,7 +15949,7 @@
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>21</v>
@@ -15941,20 +15961,16 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>344</v>
+        <v>598</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>345</v>
+        <v>599</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>21</v>
       </c>
@@ -16002,13 +16018,13 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>349</v>
+        <v>597</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>21</v>
@@ -16017,27 +16033,27 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>21</v>
+        <v>601</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>350</v>
+        <v>602</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>351</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16048,7 +16064,7 @@
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>21</v>
@@ -16060,20 +16076,16 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>390</v>
+        <v>604</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>21</v>
       </c>
@@ -16121,13 +16133,13 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>357</v>
+        <v>603</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>21</v>
@@ -16142,21 +16154,21 @@
         <v>21</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>358</v>
+        <v>602</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16176,16 +16188,16 @@
         <v>21</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16236,7 +16248,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16251,13 +16263,13 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16266,12 +16278,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>627</v>
+        <v>612</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>627</v>
+        <v>612</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16282,28 +16294,30 @@
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J116" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I116" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K116" t="s" s="2">
-        <v>628</v>
+        <v>276</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
       </c>
@@ -16351,13 +16365,13 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>627</v>
+        <v>612</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>21</v>
@@ -16366,13 +16380,13 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>632</v>
+        <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -16381,12 +16395,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16394,13 +16408,13 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>21</v>
@@ -16409,15 +16423,17 @@
         <v>21</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>105</v>
+        <v>619</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>620</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>21</v>
@@ -16442,13 +16458,11 @@
         <v>21</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>21</v>
+        <v>622</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>21</v>
@@ -16466,7 +16480,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>107</v>
+        <v>618</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16478,7 +16492,7 @@
         <v>21</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>21</v>
@@ -16487,7 +16501,7 @@
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>108</v>
+        <v>623</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>21</v>
@@ -16498,21 +16512,21 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>21</v>
@@ -16524,17 +16538,15 @@
         <v>21</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>21</v>
@@ -16571,31 +16583,31 @@
         <v>21</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>21</v>
@@ -16615,21 +16627,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>21</v>
@@ -16638,19 +16650,19 @@
         <v>21</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>637</v>
+        <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>638</v>
+        <v>112</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>639</v>
+        <v>113</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>640</v>
+        <v>114</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16688,31 +16700,31 @@
         <v>21</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>641</v>
+        <v>118</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>21</v>
@@ -16721,21 +16733,21 @@
         <v>21</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>642</v>
+        <v>108</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16743,7 +16755,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>90</v>
@@ -16758,16 +16770,20 @@
         <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>241</v>
+        <v>144</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>644</v>
+        <v>380</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>21</v>
       </c>
@@ -16815,13 +16831,13 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>646</v>
+        <v>309</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>21</v>
@@ -16836,21 +16852,21 @@
         <v>21</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>647</v>
+        <v>310</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>191</v>
+        <v>311</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16858,28 +16874,28 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>269</v>
+        <v>104</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>649</v>
+        <v>105</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>650</v>
+        <v>106</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16930,10 +16946,10 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>651</v>
+        <v>107</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>90</v>
@@ -16942,7 +16958,7 @@
         <v>21</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>21</v>
@@ -16951,35 +16967,35 @@
         <v>21</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>652</v>
+        <v>108</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>653</v>
+        <v>628</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>653</v>
+        <v>628</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>21</v>
@@ -16988,16 +17004,16 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>654</v>
+        <v>111</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>655</v>
+        <v>112</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>656</v>
+        <v>113</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>657</v>
+        <v>114</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17035,17 +17051,19 @@
         <v>21</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AC122" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="AD122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>408</v>
+        <v>117</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>653</v>
+        <v>118</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17057,16 +17075,16 @@
         <v>21</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>659</v>
+        <v>21</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>660</v>
+        <v>108</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>21</v>
@@ -17077,23 +17095,21 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>661</v>
+        <v>629</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>662</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>91</v>
@@ -17102,21 +17118,23 @@
         <v>21</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>663</v>
+        <v>132</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>655</v>
+        <v>315</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>656</v>
+        <v>316</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O123" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
       </c>
@@ -17164,13 +17182,13 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>653</v>
+        <v>319</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>21</v>
@@ -17179,31 +17197,29 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>659</v>
+        <v>21</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>660</v>
+        <v>320</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>21</v>
+        <v>321</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>664</v>
+        <v>630</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>21</v>
       </c>
@@ -17212,7 +17228,7 @@
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>91</v>
@@ -17221,19 +17237,19 @@
         <v>21</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>666</v>
+        <v>104</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>655</v>
+        <v>323</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>656</v>
+        <v>324</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>657</v>
+        <v>325</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17283,13 +17299,13 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>653</v>
+        <v>326</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>21</v>
@@ -17298,40 +17314,38 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>659</v>
+        <v>21</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>660</v>
+        <v>327</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>667</v>
+        <v>631</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>668</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>91</v>
@@ -17340,21 +17354,21 @@
         <v>21</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>669</v>
+        <v>166</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>655</v>
+        <v>330</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>21</v>
       </c>
@@ -17402,13 +17416,13 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>653</v>
+        <v>333</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>21</v>
@@ -17417,31 +17431,29 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>659</v>
+        <v>21</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>660</v>
+        <v>334</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>670</v>
+        <v>632</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C126" t="s" s="2">
-        <v>671</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>21</v>
       </c>
@@ -17450,7 +17462,7 @@
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>91</v>
@@ -17459,21 +17471,21 @@
         <v>21</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>672</v>
+        <v>104</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>655</v>
+        <v>337</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>21</v>
       </c>
@@ -17521,13 +17533,13 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>653</v>
+        <v>340</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>21</v>
@@ -17536,31 +17548,29 @@
         <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>659</v>
+        <v>21</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>660</v>
+        <v>341</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>673</v>
+        <v>633</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C127" t="s" s="2">
-        <v>674</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>21</v>
       </c>
@@ -17569,30 +17579,32 @@
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K127" t="s" s="2">
-        <v>675</v>
+        <v>344</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>655</v>
+        <v>345</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>656</v>
+        <v>346</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>21</v>
       </c>
@@ -17640,42 +17652,42 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>653</v>
+        <v>349</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>676</v>
+        <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>659</v>
+        <v>21</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>660</v>
+        <v>350</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>677</v>
+        <v>634</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>677</v>
+        <v>634</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17695,19 +17707,23 @@
         <v>21</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>678</v>
+        <v>104</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>679</v>
+        <v>390</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
       </c>
@@ -17755,7 +17771,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>677</v>
+        <v>357</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17773,24 +17789,24 @@
         <v>21</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>681</v>
+        <v>21</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>682</v>
+        <v>358</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>21</v>
+        <v>359</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>683</v>
+        <v>635</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>683</v>
+        <v>635</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17801,7 +17817,7 @@
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>21</v>
@@ -17813,13 +17829,13 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>104</v>
+        <v>636</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>105</v>
+        <v>637</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>106</v>
+        <v>638</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17870,28 +17886,28 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>107</v>
+        <v>635</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>21</v>
+        <v>639</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>108</v>
+        <v>640</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>21</v>
@@ -17900,26 +17916,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
-        <v>684</v>
+        <v>641</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>684</v>
+        <v>641</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>21</v>
@@ -17928,17 +17944,15 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>111</v>
+        <v>642</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>112</v>
+        <v>643</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>21</v>
@@ -17987,7 +18001,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>118</v>
+        <v>641</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17999,16 +18013,16 @@
         <v>21</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>21</v>
+        <v>645</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>21</v>
+        <v>646</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>108</v>
+        <v>647</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>21</v>
@@ -18019,46 +18033,42 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>685</v>
+        <v>648</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>685</v>
+        <v>648</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>686</v>
+        <v>21</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>687</v>
+        <v>105</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>689</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>21</v>
       </c>
@@ -18106,19 +18116,19 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>690</v>
+        <v>107</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>21</v>
@@ -18127,7 +18137,7 @@
         <v>21</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>191</v>
+        <v>108</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>21</v>
@@ -18138,21 +18148,21 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>691</v>
+        <v>649</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>691</v>
+        <v>649</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>21</v>
@@ -18164,16 +18174,16 @@
         <v>21</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>678</v>
+        <v>111</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>692</v>
+        <v>112</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>693</v>
+        <v>113</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>694</v>
+        <v>114</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18211,31 +18221,31 @@
         <v>21</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>691</v>
+        <v>118</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>21</v>
@@ -18244,7 +18254,7 @@
         <v>21</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>695</v>
+        <v>108</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>21</v>
@@ -18255,10 +18265,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>696</v>
+        <v>650</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>696</v>
+        <v>650</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18278,18 +18288,20 @@
         <v>21</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>104</v>
+        <v>651</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>105</v>
+        <v>652</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>21</v>
@@ -18338,7 +18350,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>107</v>
+        <v>655</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18350,7 +18362,7 @@
         <v>21</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>21</v>
@@ -18359,32 +18371,32 @@
         <v>21</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>108</v>
+        <v>656</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>697</v>
+        <v>657</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>697</v>
+        <v>657</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>21</v>
@@ -18393,20 +18405,18 @@
         <v>21</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>21</v>
@@ -18455,19 +18465,19 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>118</v>
+        <v>660</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>21</v>
@@ -18476,57 +18486,53 @@
         <v>21</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>108</v>
+        <v>661</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
-        <v>698</v>
+        <v>662</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>698</v>
+        <v>662</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>686</v>
+        <v>21</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I135" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J135" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>111</v>
+        <v>269</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>689</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>21</v>
       </c>
@@ -18574,19 +18580,19 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>690</v>
+        <v>665</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>21</v>
@@ -18595,21 +18601,21 @@
         <v>21</v>
       </c>
       <c r="AM135" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO135" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>699</v>
+        <v>667</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>699</v>
+        <v>667</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18617,13 +18623,13 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>21</v>
@@ -18632,15 +18638,17 @@
         <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>700</v>
+        <v>668</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>701</v>
+        <v>669</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N136" s="2"/>
+        <v>670</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>21</v>
@@ -18677,40 +18685,38 @@
         <v>21</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>699</v>
+        <v>667</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>703</v>
+        <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>21</v>
+        <v>673</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>704</v>
+        <v>674</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>21</v>
@@ -18719,14 +18725,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
-        <v>705</v>
+        <v>675</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="C137" s="2"/>
+        <v>667</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>676</v>
+      </c>
       <c r="D137" t="s" s="2">
         <v>21</v>
       </c>
@@ -18735,10 +18743,10 @@
         <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>21</v>
@@ -18747,15 +18755,17 @@
         <v>21</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>706</v>
+        <v>677</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>707</v>
+        <v>669</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>670</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>21</v>
@@ -18804,13 +18814,13 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>705</v>
+        <v>667</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>21</v>
@@ -18819,13 +18829,13 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>21</v>
+        <v>673</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>709</v>
+        <v>674</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
@@ -18834,14 +18844,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="138" hidden="true">
+    <row r="138">
       <c r="A138" t="s" s="2">
-        <v>710</v>
+        <v>678</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C138" s="2"/>
+        <v>667</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>679</v>
+      </c>
       <c r="D138" t="s" s="2">
         <v>21</v>
       </c>
@@ -18850,10 +18862,10 @@
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>21</v>
@@ -18862,15 +18874,17 @@
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>706</v>
+        <v>680</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>711</v>
+        <v>669</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="N138" s="2"/>
+        <v>670</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>21</v>
@@ -18919,28 +18933,28 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>710</v>
+        <v>667</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>102</v>
+        <v>681</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>21</v>
+        <v>673</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>709</v>
+        <v>674</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>21</v>
@@ -18951,10 +18965,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>713</v>
+        <v>682</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>713</v>
+        <v>682</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18965,7 +18979,7 @@
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>21</v>
@@ -18977,20 +18991,16 @@
         <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>231</v>
+        <v>683</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>714</v>
+        <v>684</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>717</v>
-      </c>
+        <v>685</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>21</v>
       </c>
@@ -19038,7 +19048,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>713</v>
+        <v>682</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19056,10 +19066,10 @@
         <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>718</v>
+        <v>686</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>719</v>
+        <v>687</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
@@ -19070,10 +19080,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>720</v>
+        <v>688</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>720</v>
+        <v>688</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19096,17 +19106,15 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>721</v>
+        <v>104</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>722</v>
+        <v>105</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>724</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>21</v>
@@ -19155,7 +19163,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>720</v>
+        <v>107</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19167,41 +19175,41 @@
         <v>21</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>725</v>
+        <v>21</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>726</v>
+        <v>108</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>727</v>
+        <v>21</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>728</v>
+        <v>689</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>728</v>
+        <v>689</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>21</v>
@@ -19213,15 +19221,17 @@
         <v>21</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>700</v>
+        <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>729</v>
+        <v>112</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>21</v>
@@ -19270,76 +19280,78 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>728</v>
+        <v>118</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>703</v>
+        <v>119</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>731</v>
+        <v>21</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>732</v>
+        <v>108</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>733</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>734</v>
+        <v>690</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>734</v>
+        <v>690</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>21</v>
+        <v>691</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>706</v>
+        <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>735</v>
+        <v>692</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>736</v>
+        <v>693</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>694</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
       </c>
@@ -19387,28 +19399,28 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>734</v>
+        <v>695</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>738</v>
+        <v>21</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>739</v>
+        <v>191</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>21</v>
@@ -19419,10 +19431,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>740</v>
+        <v>696</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>740</v>
+        <v>696</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19445,15 +19457,17 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>507</v>
+        <v>683</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>741</v>
+        <v>697</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>698</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>699</v>
+      </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>21</v>
@@ -19502,7 +19516,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>740</v>
+        <v>696</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19523,10 +19537,10 @@
         <v>21</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>743</v>
+        <v>700</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>564</v>
+        <v>21</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>21</v>
@@ -19534,10 +19548,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>744</v>
+        <v>701</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>744</v>
+        <v>701</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19560,13 +19574,13 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>678</v>
+        <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>745</v>
+        <v>105</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>746</v>
+        <v>106</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19617,7 +19631,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>744</v>
+        <v>107</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19629,16 +19643,16 @@
         <v>21</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>747</v>
+        <v>21</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>748</v>
+        <v>108</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>21</v>
@@ -19649,21 +19663,21 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>749</v>
+        <v>702</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>749</v>
+        <v>702</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>21</v>
@@ -19675,15 +19689,17 @@
         <v>21</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N145" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>21</v>
@@ -19732,19 +19748,19 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>21</v>
@@ -19764,14 +19780,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>750</v>
+        <v>703</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>750</v>
+        <v>703</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>110</v>
+        <v>691</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -19784,24 +19800,26 @@
         <v>21</v>
       </c>
       <c r="I146" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>112</v>
+        <v>692</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>113</v>
+        <v>693</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O146" s="2"/>
+      <c r="O146" t="s" s="2">
+        <v>694</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>21</v>
       </c>
@@ -19849,7 +19867,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>118</v>
+        <v>695</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19870,7 +19888,7 @@
         <v>21</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>21</v>
@@ -19881,46 +19899,42 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>751</v>
+        <v>704</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>751</v>
+        <v>704</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>686</v>
+        <v>21</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>111</v>
+        <v>705</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>687</v>
+        <v>706</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>689</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>21</v>
       </c>
@@ -19968,19 +19982,19 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>119</v>
+        <v>708</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>21</v>
@@ -19989,7 +20003,7 @@
         <v>21</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>191</v>
+        <v>709</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>21</v>
@@ -20000,10 +20014,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>752</v>
+        <v>710</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>752</v>
+        <v>710</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20011,7 +20025,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>90</v>
@@ -20026,17 +20040,15 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>753</v>
+        <v>711</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>754</v>
+        <v>712</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>756</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>21</v>
@@ -20061,13 +20073,13 @@
         <v>21</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>757</v>
+        <v>21</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>758</v>
+        <v>21</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>21</v>
@@ -20085,10 +20097,10 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>752</v>
+        <v>710</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>90</v>
@@ -20103,24 +20115,24 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>747</v>
+        <v>21</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>759</v>
+        <v>714</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>760</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>761</v>
+        <v>715</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>761</v>
+        <v>715</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20143,13 +20155,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>295</v>
+        <v>711</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>762</v>
+        <v>716</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>763</v>
+        <v>717</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20176,13 +20188,13 @@
         <v>21</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>764</v>
+        <v>21</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>765</v>
+        <v>21</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>21</v>
@@ -20200,7 +20212,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>761</v>
+        <v>715</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20218,24 +20230,24 @@
         <v>21</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>766</v>
+        <v>21</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>767</v>
+        <v>714</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>768</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>769</v>
+        <v>718</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>769</v>
+        <v>718</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20258,16 +20270,20 @@
         <v>21</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>770</v>
+        <v>231</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>771</v>
+        <v>719</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
+        <v>720</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>21</v>
       </c>
@@ -20315,7 +20331,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>769</v>
+        <v>718</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20330,13 +20346,13 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>773</v>
+        <v>21</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>766</v>
+        <v>723</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>774</v>
+        <v>724</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>21</v>
@@ -20347,21 +20363,21 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>776</v>
+        <v>21</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>21</v>
@@ -20373,16 +20389,16 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>777</v>
+        <v>726</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>778</v>
+        <v>727</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>779</v>
+        <v>728</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>780</v>
+        <v>729</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20432,13 +20448,13 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>775</v>
+        <v>725</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>21</v>
@@ -20450,24 +20466,24 @@
         <v>21</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>21</v>
+        <v>730</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>781</v>
+        <v>731</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>21</v>
+        <v>732</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>782</v>
+        <v>733</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>782</v>
+        <v>733</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20478,7 +20494,7 @@
         <v>80</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>21</v>
@@ -20490,17 +20506,15 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>783</v>
+        <v>705</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>784</v>
+        <v>734</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>786</v>
-      </c>
+        <v>735</v>
+      </c>
+      <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>21</v>
@@ -20549,38 +20563,1317 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="153" hidden="true">
+      <c r="A153" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="154" hidden="true">
+      <c r="A154" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="155" hidden="true">
+      <c r="A155" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
+      <c r="P155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="156" hidden="true">
+      <c r="A156" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+      <c r="P156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157" hidden="true">
+      <c r="A157" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O157" s="2"/>
+      <c r="P157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158" hidden="true">
+      <c r="A158" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="159" hidden="true">
+      <c r="A159" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="160" hidden="true">
+      <c r="A160" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="N160" s="2"/>
+      <c r="O160" s="2"/>
+      <c r="P160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO160" t="s" s="2">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="161" hidden="true">
+      <c r="A161" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="N161" s="2"/>
+      <c r="O161" s="2"/>
+      <c r="P161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO161" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="162" hidden="true">
+      <c r="A162" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="E162" s="2"/>
+      <c r="F162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K162" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="AG152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH152" t="s" s="2">
+      <c r="L162" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="O162" s="2"/>
+      <c r="P162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q162" s="2"/>
+      <c r="R162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH162" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
+      <c r="AI162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK152" t="s" s="2">
+      <c r="AK162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AN162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO162" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="163" hidden="true">
+      <c r="A163" t="s" s="2">
         <v>787</v>
       </c>
-      <c r="AL152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM152" t="s" s="2">
+      <c r="B163" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="C163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E163" s="2"/>
+      <c r="F163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K163" t="s" s="2">
         <v>788</v>
       </c>
-      <c r="AN152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO152" t="s" s="2">
+      <c r="L163" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="M163" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="O163" s="2"/>
+      <c r="P163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q163" s="2"/>
+      <c r="R163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF163" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AG163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK163" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="AL163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM163" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="AN163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO163" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO152">
+  <autoFilter ref="A1:AO163">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -20590,7 +21883,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI151">
+  <conditionalFormatting sqref="A2:AI162">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1304,7 +1304,7 @@
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>Quelle der Information. Bedeutung: false: Verordnung durch den Planeintrag erstellenden GDA | true: Fremdmedikation oder Eigenmedikation des Patienten.</t>
+    <t>Kennzeichnet, ob die Medikationsinformation berichtet wurde. Bedeutung: false: Verordnung durch den Planeintrag erstellenden GDA | true: Fremdmedikation oder Eigenmedikation des Patienten.</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6040" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6040" uniqueCount="796">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}allDosagesSameCategory:Alle Dosierungsanweisungen eines MedicationRequest müssen dieselbe Dosierungskategorie aufweisen. {dosageInstruction.extension.where(url = 'https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category').value.coding.code.distinct().count() = 1}FirstDosageSequenceNumberExists:Wenn mehrere Dosierungsanweisungen vorhanden sind, muss mindestens eine davon die Sequenznummer 1 haben. {dosageInstruction.count() &lt;= 1 or dosageInstruction.sequence.where($this = 1).exists()}at-emed-planeintrag-status-reason-beim-absetzen:Bei Status 'stopped' oder 'entered-in-error' muss ein statusReason angegeben werden. {(status = 'stopped' or status = 'entered-in-error') implies statusReason.coding.code.exists()}e-med-continuous-medication-effectiveDosePeriod:Eine Dauermedikation (courseOfTherapyType = #continuous) darf kein Enddatum besitzen. {courseOfTherapyType.where(coding.code='continuous' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists().not()}e-med-acute-medication-effectiveDosePeriod:Eine Akutmedikation (courseOfTherapyType = #acute) muss ein Enddatum besitzen. {courseOfTherapyType.where(coding.code='acute' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}allDosagesSameCategory:Alle Dosierungsanweisungen eines MedicationRequest müssen dieselbe Dosierungskategorie aufweisen. {dosageInstruction.extension.where(url = 'https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category').value.coding.code.distinct().count() = 1}FirstDosageSequenceNumberExists:Wenn mehrere Dosierungsanweisungen vorhanden sind, muss mindestens eine davon die Sequenznummer 1 haben. {dosageInstruction.count() &lt;= 1 or dosageInstruction.sequence.where($this = 1).exists()}at-emed-planeintrag-status-reason-beim-absetzen-oder-pausieren:Bei Status 'stopped' oder 'on-hold' muss ein statusReason angegeben werden. {(status = 'stopped' or status = 'on-hold') implies statusReason.coding.code.exists()}e-med-acute-medication-effectiveDosePeriod:Eine Akutmedikation (courseOfTherapyType = #acute) muss ein Enddatum besitzen. {courseOfTherapyType.where(coding.code='acute' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -689,7 +689,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitraum, in dem das Arzneimittel eingenommen werden soll.</t>
+    <t>Zeitraum, in dem das Arzneimittel eingenommen werden soll. Bei Dauermedikation kann optional ein Enddatum dokumentiert werden. Bei Aktumedikation ist verpflichtend ein Enddatum zu dokumentieren. Der Einnahmezeitraum muss mit den zeitlichen Einschränkungen der Dosage übereinstimmen</t>
   </si>
   <si>
     <t>R5: `MedicationRequest.effectiveDosePeriod` (new:Period)</t>
@@ -914,8 +914,8 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status des Planeintrags. Mögliche Ausprägungen: [active | on-hold | stopped | entered-in-error]. Bedeutung: active: aktuell einzunehmende Medikation | on-hold: pausierte Medikation (aktuell nicht einzunehmen) | stopped: wird nicht weiter verordnet (unabhängig ob vorzeitig abgesetzt, abgeschlossen oder Behandlungszeitraum abgelaufen   
-| entered-in-error: Fehlerhafter Planeintrag storniert und abgeschlossen.</t>
+    <t>Status des Planeintrags. Mögliche Ausprägungen: [active | on-hold | stopped | entered-in-error]. Bedeutung: active: aktuell einzunehmende Medikation | on-hold: pausierte Medikation (aktuell nicht einzunehmen) | stopped: wird nicht weiter verordnet (unabhängig ob vorzeitig abgesetzt, abgeschlossen oder Behandlungszeitraum abgelaufen)   
+| entered-in-error: fehlerhafter Planeintrag storniert und abgeschlossen</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -946,7 +946,7 @@
 </t>
   </si>
   <si>
-    <t>Reason for current status</t>
+    <t>Begründung für den Status des Planeintrags.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -973,7 +973,7 @@
     <t>MedicationRequest.statusReason.coding</t>
   </si>
   <si>
-    <t>Codierte Begründung für den Status des Planeintrags.</t>
+    <t>Codierte Begründung für den Status. Wenn status stopped oder on-hold, verpflichtend anzugeben. Existiert kein passender Code, muss "other" ausgewählt werden und ein Freitext in dokumentiert werden.</t>
   </si>
   <si>
     <t>A reference to a code defined by a terminology system.</t>
@@ -1142,7 +1142,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Ein Planeintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine Geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
+    <t>Fixer Wert: "order".</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -1176,7 +1176,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Kategorie zur Unterscheidung eines Planeintrags von einer geplanten Abgabe (beide haben intent order)</t>
+    <t>Kategorie zur Unterscheidung eines Planeintrags von einer Geplanten Abgabe (beide haben intent order).</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -1237,7 +1237,7 @@
     <t>MedicationRequest.category.text</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>Plain text representation of the concept</t>
   </si>
   <si>
     <t>MedicationRequest.priority</t>
@@ -1314,7 +1314,7 @@
 </t>
   </si>
   <si>
-    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als logische Referenz dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als conditional reference dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -1484,6 +1484,9 @@
     <t>MedicationRequest.subject.identifier.use</t>
   </si>
   <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
     <t>The purpose of this identifier.</t>
   </si>
   <si>
@@ -1679,7 +1682,7 @@
     <t>MedicationRequest.authoredOn</t>
   </si>
   <si>
-    <t>Datum der Verordnung des Planeintrags.</t>
+    <t>Datum der Erstellung des Planeintrags.</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -1707,7 +1710,7 @@
 </t>
   </si>
   <si>
-    <t>GDA welcher den Planeintrag zuletzt bearbeitet hat und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
+    <t>GDA, welcher den Planeintrag zuletzt bearbeitet hat und für den Inhalt verantwortlich ist.</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1931,7 +1934,7 @@
     <t>MedicationRequest.groupIdentifier</t>
   </si>
   <si>
-    <t>Fachliche Begründung: Eine Rezept-Klammer wird erst bei der Erstellung geplanter Abgaben benötigt und nicht im Planeintrag dokumentiert.</t>
+    <t>Fachliche Begründung: Eine Rezept-Klammer wird erst bei der Erstellung Geplanter Abgaben benötigt und nicht im Planeintrag dokumentiert.</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -1949,7 +1952,7 @@
     <t>MedicationRequest.courseOfTherapyType</t>
   </si>
   <si>
-    <t>Gesamtmuster der Medikamentengabe. Mögliche Ausprägungen: [continuous | acute ]</t>
+    <t>Art der Medikation. Mögliche Ausprägungen: [continuous | acute]</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>
@@ -1995,6 +1998,9 @@
   </si>
   <si>
     <t>MedicationRequest.courseOfTherapyType.text</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>MedicationRequest.insurance</t>
@@ -2153,7 +2159,7 @@
 </t>
   </si>
   <si>
-    <t>Fachliche Begründung: Abgabedetails werden in der geplanten Abgabe und nicht im Planeintrag dokumentiert.</t>
+    <t>Fachliche Begründung: Abgabedetails werden in der Geplanten Abgabe und nicht im Planeintrag dokumentiert.</t>
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
@@ -12460,16 +12466,16 @@
         <v>166</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>390</v>
+        <v>467</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -12497,10 +12503,10 @@
         <v>187</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
@@ -12518,7 +12524,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12539,7 +12545,7 @@
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12550,10 +12556,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12579,16 +12585,16 @@
         <v>295</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -12616,10 +12622,10 @@
         <v>148</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>21</v>
@@ -12637,7 +12643,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12658,21 +12664,21 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12698,16 +12704,16 @@
         <v>132</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12720,7 +12726,7 @@
         <v>21</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>21</v>
@@ -12756,7 +12762,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12777,21 +12783,21 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12817,13 +12823,13 @@
         <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12837,7 +12843,7 @@
         <v>21</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>21</v>
@@ -12873,7 +12879,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12894,21 +12900,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12934,10 +12940,10 @@
         <v>231</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12988,7 +12994,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13009,21 +13015,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13046,16 +13052,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13105,7 +13111,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13126,21 +13132,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13254,10 +13260,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13280,16 +13286,16 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13339,7 +13345,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13354,27 +13360,27 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13397,13 +13403,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13454,7 +13460,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13469,16 +13475,16 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>21</v>
@@ -13486,10 +13492,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13515,10 +13521,10 @@
         <v>241</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13569,7 +13575,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13584,27 +13590,27 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13627,13 +13633,13 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13684,7 +13690,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13699,7 +13705,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
@@ -13708,7 +13714,7 @@
         <v>456</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>21</v>
@@ -13716,10 +13722,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13831,10 +13837,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13948,10 +13954,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14065,10 +14071,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14182,10 +14188,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14299,10 +14305,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14414,10 +14420,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14531,10 +14537,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14560,16 +14566,16 @@
         <v>166</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>390</v>
+        <v>467</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14597,10 +14603,10 @@
         <v>187</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>21</v>
@@ -14618,7 +14624,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14639,7 +14645,7 @@
         <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>21</v>
@@ -14650,10 +14656,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14679,16 +14685,16 @@
         <v>295</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14716,10 +14722,10 @@
         <v>148</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14737,7 +14743,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14758,21 +14764,21 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14798,16 +14804,16 @@
         <v>132</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -14820,7 +14826,7 @@
         <v>21</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>21</v>
@@ -14856,7 +14862,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14877,21 +14883,21 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14917,13 +14923,13 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14937,7 +14943,7 @@
         <v>21</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>21</v>
@@ -14973,7 +14979,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14994,21 +15000,21 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15034,10 +15040,10 @@
         <v>231</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15088,7 +15094,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15109,21 +15115,21 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15146,16 +15152,16 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15205,7 +15211,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15226,21 +15232,21 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15354,10 +15360,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15380,13 +15386,13 @@
         <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15437,7 +15443,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15452,16 +15458,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>21</v>
@@ -15469,10 +15475,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15498,13 +15504,13 @@
         <v>295</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15533,10 +15539,10 @@
         <v>156</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>21</v>
@@ -15554,7 +15560,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15569,13 +15575,13 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>21</v>
@@ -15586,10 +15592,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15612,13 +15618,13 @@
         <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15669,7 +15675,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15690,10 +15696,10 @@
         <v>21</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>21</v>
@@ -15701,10 +15707,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15730,13 +15736,13 @@
         <v>295</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15765,10 +15771,10 @@
         <v>156</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>21</v>
@@ -15786,7 +15792,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15801,27 +15807,27 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15844,16 +15850,16 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15903,7 +15909,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15918,16 +15924,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>21</v>
@@ -15935,10 +15941,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15961,13 +15967,13 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16018,7 +16024,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16033,13 +16039,13 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>21</v>
@@ -16050,10 +16056,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16079,10 +16085,10 @@
         <v>132</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16133,7 +16139,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16154,7 +16160,7 @@
         <v>21</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>21</v>
@@ -16165,10 +16171,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16191,13 +16197,13 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16248,7 +16254,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16263,13 +16269,13 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16280,10 +16286,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16309,14 +16315,14 @@
         <v>276</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -16365,7 +16371,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16380,13 +16386,13 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -16397,10 +16403,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16426,13 +16432,13 @@
         <v>295</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16462,7 +16468,7 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>21</v>
@@ -16480,7 +16486,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16501,7 +16507,7 @@
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>21</v>
@@ -16512,10 +16518,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16627,10 +16633,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16744,10 +16750,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16863,10 +16869,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16978,10 +16984,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17095,10 +17101,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17214,10 +17220,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17331,10 +17337,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17448,10 +17454,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17565,10 +17571,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17684,10 +17690,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17713,7 +17719,7 @@
         <v>104</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>390</v>
+        <v>636</v>
       </c>
       <c r="M128" t="s" s="2">
         <v>354</v>
@@ -17803,10 +17809,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17829,13 +17835,13 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17886,7 +17892,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17901,13 +17907,13 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>21</v>
@@ -17918,10 +17924,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17944,13 +17950,13 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18001,7 +18007,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18016,13 +18022,13 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>21</v>
@@ -18033,10 +18039,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18148,10 +18154,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18265,10 +18271,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18291,16 +18297,16 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18350,7 +18356,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18371,7 +18377,7 @@
         <v>21</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>21</v>
@@ -18382,10 +18388,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18411,10 +18417,10 @@
         <v>241</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18465,7 +18471,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18486,7 +18492,7 @@
         <v>21</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>21</v>
@@ -18497,10 +18503,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18526,10 +18532,10 @@
         <v>269</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18580,7 +18586,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>90</v>
@@ -18601,7 +18607,7 @@
         <v>21</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>21</v>
@@ -18612,10 +18618,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18638,16 +18644,16 @@
         <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18685,7 +18691,7 @@
         <v>21</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
@@ -18695,7 +18701,7 @@
         <v>408</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18710,13 +18716,13 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>21</v>
@@ -18727,13 +18733,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>21</v>
@@ -18755,16 +18761,16 @@
         <v>21</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18814,7 +18820,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18829,13 +18835,13 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
@@ -18846,13 +18852,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>21</v>
@@ -18874,16 +18880,16 @@
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18933,7 +18939,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18945,16 +18951,16 @@
         <v>21</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>21</v>
@@ -18965,10 +18971,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18991,13 +18997,13 @@
         <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19048,7 +19054,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19066,10 +19072,10 @@
         <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
@@ -19080,10 +19086,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19195,10 +19201,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19312,14 +19318,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19341,16 +19347,16 @@
         <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
@@ -19399,7 +19405,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19431,10 +19437,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19457,16 +19463,16 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19516,7 +19522,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19537,7 +19543,7 @@
         <v>21</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -19548,10 +19554,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19663,10 +19669,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19780,14 +19786,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -19809,16 +19815,16 @@
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>21</v>
@@ -19867,7 +19873,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19899,10 +19905,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19925,13 +19931,13 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19982,7 +19988,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -19994,7 +20000,7 @@
         <v>21</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>21</v>
@@ -20003,7 +20009,7 @@
         <v>21</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>21</v>
@@ -20014,10 +20020,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20040,13 +20046,13 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20097,7 +20103,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20118,7 +20124,7 @@
         <v>21</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>21</v>
@@ -20129,10 +20135,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20155,13 +20161,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20212,7 +20218,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20233,7 +20239,7 @@
         <v>21</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>21</v>
@@ -20244,10 +20250,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20273,16 +20279,16 @@
         <v>231</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>21</v>
@@ -20331,7 +20337,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20349,10 +20355,10 @@
         <v>21</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>21</v>
@@ -20363,10 +20369,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20389,16 +20395,16 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20448,7 +20454,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20466,24 +20472,24 @@
         <v>21</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20506,13 +20512,13 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20563,7 +20569,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20575,30 +20581,30 @@
         <v>21</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20621,16 +20627,16 @@
         <v>21</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -20680,7 +20686,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20698,10 +20704,10 @@
         <v>21</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>21</v>
@@ -20712,10 +20718,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20738,13 +20744,13 @@
         <v>21</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -20795,7 +20801,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -20816,10 +20822,10 @@
         <v>21</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>21</v>
@@ -20827,10 +20833,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20853,13 +20859,13 @@
         <v>21</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -20910,7 +20916,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -20928,10 +20934,10 @@
         <v>21</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>21</v>
@@ -20942,10 +20948,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21057,10 +21063,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21174,14 +21180,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21203,16 +21209,16 @@
         <v>111</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>21</v>
@@ -21261,7 +21267,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21293,10 +21299,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21319,16 +21325,16 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21357,10 +21363,10 @@
         <v>156</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>21</v>
@@ -21378,7 +21384,7 @@
         <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>90</v>
@@ -21396,24 +21402,24 @@
         <v>21</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21439,10 +21445,10 @@
         <v>295</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21472,10 +21478,10 @@
         <v>156</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>21</v>
@@ -21493,7 +21499,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21511,24 +21517,24 @@
         <v>21</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21551,13 +21557,13 @@
         <v>21</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21608,7 +21614,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21623,13 +21629,13 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>21</v>
@@ -21640,14 +21646,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21666,16 +21672,16 @@
         <v>21</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -21725,7 +21731,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21746,7 +21752,7 @@
         <v>21</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>21</v>
@@ -21757,10 +21763,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21783,16 +21789,16 @@
         <v>21</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21842,7 +21848,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -21857,13 +21863,13 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6040" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6040" uniqueCount="797">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
 </t>
   </si>
   <si>
-    <t>Planeintrag</t>
+    <t>Ordering of medication for patient or group</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>
@@ -689,7 +689,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitraum, in dem das Arzneimittel eingenommen werden soll. Bei Dauermedikation kann optional ein Enddatum dokumentiert werden. Bei Aktumedikation ist verpflichtend ein Enddatum zu dokumentieren. Der Einnahmezeitraum muss mit den zeitlichen Einschränkungen der Dosage übereinstimmen</t>
+    <t>Zeitraum, in dem das Arzneimittel eingenommen werden soll. Bei Dauermedikation kann optional ein Enddatum dokumentiert werden. Bei Aktumedikation ist verpflichtend ein Enddatum zu dokumentieren. Der Einnahmezeitraum muss mit den zeitlichen Einschränkungen der Dosage übereinstimmen.</t>
   </si>
   <si>
     <t>R5: `MedicationRequest.effectiveDosePeriod` (new:Period)</t>
@@ -915,7 +915,7 @@
   </si>
   <si>
     <t>Status des Planeintrags. Mögliche Ausprägungen: [active | on-hold | stopped | entered-in-error]. Bedeutung: active: aktuell einzunehmende Medikation | on-hold: pausierte Medikation (aktuell nicht einzunehmen) | stopped: wird nicht weiter verordnet (unabhängig ob vorzeitig abgesetzt, abgeschlossen oder Behandlungszeitraum abgelaufen)   
-| entered-in-error: fehlerhafter Planeintrag storniert und abgeschlossen</t>
+| entered-in-error: fehlerhafter Planeintrag storniert</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -1226,6 +1226,9 @@
   </si>
   <si>
     <t>MedicationRequest.category.coding.code</t>
+  </si>
+  <si>
+    <t>Planeintrag</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding.display</t>
@@ -9800,7 +9803,7 @@
         <v>21</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>21</v>
@@ -9871,10 +9874,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9988,10 +9991,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10107,10 +10110,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10136,7 +10139,7 @@
         <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M63" t="s" s="2">
         <v>354</v>
@@ -10226,10 +10229,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10255,10 +10258,10 @@
         <v>166</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10288,10 +10291,10 @@
         <v>187</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -10309,7 +10312,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10324,16 +10327,16 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
@@ -10341,10 +10344,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10370,13 +10373,13 @@
         <v>344</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10426,7 +10429,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10447,7 +10450,7 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -10458,10 +10461,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10487,10 +10490,10 @@
         <v>344</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10529,17 +10532,17 @@
         <v>21</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10560,7 +10563,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -10571,13 +10574,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>21</v>
@@ -10602,10 +10605,10 @@
         <v>344</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10656,7 +10659,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10677,7 +10680,7 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10688,10 +10691,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10714,16 +10717,16 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10773,7 +10776,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>90</v>
@@ -10788,27 +10791,27 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10920,10 +10923,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11037,10 +11040,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11066,13 +11069,13 @@
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11122,7 +11125,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11131,7 +11134,7 @@
         <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>102</v>
@@ -11154,10 +11157,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11183,13 +11186,13 @@
         <v>132</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11218,10 +11221,10 @@
         <v>148</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -11239,7 +11242,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11271,10 +11274,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11300,13 +11303,13 @@
         <v>276</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11356,7 +11359,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11377,7 +11380,7 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -11388,10 +11391,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11417,13 +11420,13 @@
         <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11473,7 +11476,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11505,10 +11508,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11531,16 +11534,16 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11590,7 +11593,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -11605,27 +11608,27 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11737,10 +11740,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11854,10 +11857,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11883,13 +11886,13 @@
         <v>104</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11939,7 +11942,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11948,7 +11951,7 @@
         <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>102</v>
@@ -11971,10 +11974,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12000,13 +12003,13 @@
         <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12035,10 +12038,10 @@
         <v>148</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>21</v>
@@ -12056,7 +12059,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12088,10 +12091,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12117,13 +12120,13 @@
         <v>276</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12173,7 +12176,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12194,7 +12197,7 @@
         <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -12205,10 +12208,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12320,10 +12323,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12437,10 +12440,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12466,16 +12469,16 @@
         <v>166</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -12503,10 +12506,10 @@
         <v>187</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
@@ -12524,7 +12527,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12545,7 +12548,7 @@
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12556,10 +12559,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12585,16 +12588,16 @@
         <v>295</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -12622,10 +12625,10 @@
         <v>148</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>21</v>
@@ -12643,7 +12646,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12664,21 +12667,21 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12704,16 +12707,16 @@
         <v>132</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12726,7 +12729,7 @@
         <v>21</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>21</v>
@@ -12762,7 +12765,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12783,21 +12786,21 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12823,13 +12826,13 @@
         <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12843,7 +12846,7 @@
         <v>21</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>21</v>
@@ -12879,7 +12882,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12900,21 +12903,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12940,10 +12943,10 @@
         <v>231</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12994,7 +12997,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13015,21 +13018,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13052,16 +13055,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13111,7 +13114,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13132,21 +13135,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13172,13 +13175,13 @@
         <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13228,7 +13231,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13260,10 +13263,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13286,16 +13289,16 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13345,7 +13348,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13360,27 +13363,27 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13403,13 +13406,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13460,7 +13463,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13475,16 +13478,16 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>21</v>
@@ -13492,10 +13495,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13521,10 +13524,10 @@
         <v>241</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13575,7 +13578,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13590,27 +13593,27 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13633,13 +13636,13 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13690,7 +13693,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13705,16 +13708,16 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>21</v>
@@ -13722,10 +13725,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13837,10 +13840,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13954,10 +13957,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13983,13 +13986,13 @@
         <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14039,7 +14042,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14048,7 +14051,7 @@
         <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>102</v>
@@ -14071,10 +14074,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14100,13 +14103,13 @@
         <v>132</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14135,10 +14138,10 @@
         <v>148</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -14156,7 +14159,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14188,10 +14191,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14217,13 +14220,13 @@
         <v>276</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14273,7 +14276,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14294,7 +14297,7 @@
         <v>21</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>21</v>
@@ -14305,10 +14308,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14420,10 +14423,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14537,10 +14540,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14566,16 +14569,16 @@
         <v>166</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14603,10 +14606,10 @@
         <v>187</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>21</v>
@@ -14624,7 +14627,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14645,7 +14648,7 @@
         <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>21</v>
@@ -14656,10 +14659,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14685,16 +14688,16 @@
         <v>295</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14722,10 +14725,10 @@
         <v>148</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14743,7 +14746,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14764,21 +14767,21 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14804,16 +14807,16 @@
         <v>132</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -14826,7 +14829,7 @@
         <v>21</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>21</v>
@@ -14862,7 +14865,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14883,21 +14886,21 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14923,13 +14926,13 @@
         <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14943,7 +14946,7 @@
         <v>21</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>21</v>
@@ -14979,7 +14982,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15000,21 +15003,21 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15040,10 +15043,10 @@
         <v>231</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15094,7 +15097,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15115,21 +15118,21 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15152,16 +15155,16 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15211,7 +15214,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15232,21 +15235,21 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15272,13 +15275,13 @@
         <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15328,7 +15331,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15360,10 +15363,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15386,13 +15389,13 @@
         <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15443,7 +15446,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15458,16 +15461,16 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>21</v>
@@ -15475,10 +15478,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15504,13 +15507,13 @@
         <v>295</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15539,10 +15542,10 @@
         <v>156</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>21</v>
@@ -15560,7 +15563,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15575,13 +15578,13 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>21</v>
@@ -15592,10 +15595,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15618,13 +15621,13 @@
         <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15675,7 +15678,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15696,10 +15699,10 @@
         <v>21</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>21</v>
@@ -15707,10 +15710,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15736,13 +15739,13 @@
         <v>295</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15771,10 +15774,10 @@
         <v>156</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>21</v>
@@ -15792,7 +15795,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15807,27 +15810,27 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15850,16 +15853,16 @@
         <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15909,7 +15912,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15924,16 +15927,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>21</v>
@@ -15941,10 +15944,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15967,13 +15970,13 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16024,7 +16027,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16039,13 +16042,13 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>21</v>
@@ -16056,10 +16059,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16085,10 +16088,10 @@
         <v>132</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16139,7 +16142,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16160,7 +16163,7 @@
         <v>21</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>21</v>
@@ -16171,10 +16174,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16197,13 +16200,13 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16254,7 +16257,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16269,13 +16272,13 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16286,10 +16289,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16315,14 +16318,14 @@
         <v>276</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -16371,7 +16374,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16386,13 +16389,13 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -16403,10 +16406,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16432,13 +16435,13 @@
         <v>295</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16468,7 +16471,7 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>21</v>
@@ -16486,7 +16489,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16507,7 +16510,7 @@
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>21</v>
@@ -16518,10 +16521,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16633,10 +16636,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16750,10 +16753,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16869,10 +16872,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16984,10 +16987,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17101,10 +17104,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17220,10 +17223,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17337,10 +17340,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17454,10 +17457,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17571,10 +17574,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17690,10 +17693,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17719,7 +17722,7 @@
         <v>104</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M128" t="s" s="2">
         <v>354</v>
@@ -17809,10 +17812,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17835,13 +17838,13 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17892,7 +17895,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17907,13 +17910,13 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>21</v>
@@ -17924,10 +17927,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17950,13 +17953,13 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18007,7 +18010,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18022,13 +18025,13 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>21</v>
@@ -18039,10 +18042,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18154,10 +18157,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18271,10 +18274,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18297,16 +18300,16 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18356,7 +18359,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18377,7 +18380,7 @@
         <v>21</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>21</v>
@@ -18388,10 +18391,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18417,10 +18420,10 @@
         <v>241</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18471,7 +18474,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18492,7 +18495,7 @@
         <v>21</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>21</v>
@@ -18503,10 +18506,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18532,10 +18535,10 @@
         <v>269</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18586,7 +18589,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>90</v>
@@ -18607,7 +18610,7 @@
         <v>21</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>21</v>
@@ -18618,10 +18621,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18644,16 +18647,16 @@
         <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18691,17 +18694,17 @@
         <v>21</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18716,13 +18719,13 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>21</v>
@@ -18733,13 +18736,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>21</v>
@@ -18761,16 +18764,16 @@
         <v>21</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18820,7 +18823,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18835,13 +18838,13 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
@@ -18852,13 +18855,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>21</v>
@@ -18880,16 +18883,16 @@
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18939,7 +18942,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18951,16 +18954,16 @@
         <v>21</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>21</v>
@@ -18971,10 +18974,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18997,13 +19000,13 @@
         <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19054,7 +19057,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19072,10 +19075,10 @@
         <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
@@ -19086,10 +19089,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19201,10 +19204,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19318,14 +19321,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19347,16 +19350,16 @@
         <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
@@ -19405,7 +19408,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19437,10 +19440,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19463,16 +19466,16 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19522,7 +19525,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19543,7 +19546,7 @@
         <v>21</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -19554,10 +19557,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19669,10 +19672,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19786,14 +19789,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -19815,16 +19818,16 @@
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>21</v>
@@ -19873,7 +19876,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19905,10 +19908,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19931,13 +19934,13 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19988,7 +19991,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20000,7 +20003,7 @@
         <v>21</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>21</v>
@@ -20009,7 +20012,7 @@
         <v>21</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>21</v>
@@ -20020,10 +20023,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20046,13 +20049,13 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20103,7 +20106,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20124,7 +20127,7 @@
         <v>21</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>21</v>
@@ -20135,10 +20138,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20161,13 +20164,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20218,7 +20221,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20239,7 +20242,7 @@
         <v>21</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>21</v>
@@ -20250,10 +20253,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20279,16 +20282,16 @@
         <v>231</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>21</v>
@@ -20337,7 +20340,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20355,10 +20358,10 @@
         <v>21</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>21</v>
@@ -20369,10 +20372,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20395,16 +20398,16 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20454,7 +20457,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20472,24 +20475,24 @@
         <v>21</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20512,13 +20515,13 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20569,7 +20572,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20581,30 +20584,30 @@
         <v>21</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20627,16 +20630,16 @@
         <v>21</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -20686,7 +20689,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20704,10 +20707,10 @@
         <v>21</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>21</v>
@@ -20718,10 +20721,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20744,13 +20747,13 @@
         <v>21</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -20801,7 +20804,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -20822,10 +20825,10 @@
         <v>21</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>21</v>
@@ -20833,10 +20836,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20859,13 +20862,13 @@
         <v>21</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -20916,7 +20919,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -20934,10 +20937,10 @@
         <v>21</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>21</v>
@@ -20948,10 +20951,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21063,10 +21066,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21180,14 +21183,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21209,16 +21212,16 @@
         <v>111</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>21</v>
@@ -21267,7 +21270,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21299,10 +21302,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21325,16 +21328,16 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21363,10 +21366,10 @@
         <v>156</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>21</v>
@@ -21384,7 +21387,7 @@
         <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>90</v>
@@ -21402,24 +21405,24 @@
         <v>21</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21445,10 +21448,10 @@
         <v>295</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21478,10 +21481,10 @@
         <v>156</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>21</v>
@@ -21499,7 +21502,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21517,24 +21520,24 @@
         <v>21</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21557,13 +21560,13 @@
         <v>21</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21614,7 +21617,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21629,13 +21632,13 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>21</v>
@@ -21646,14 +21649,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21672,16 +21675,16 @@
         <v>21</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -21731,7 +21734,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21752,7 +21755,7 @@
         <v>21</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>21</v>
@@ -21763,10 +21766,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21789,16 +21792,16 @@
         <v>21</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21848,7 +21851,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -21863,13 +21866,13 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6040" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6040" uniqueCount="796">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1317,7 +1317,7 @@
 </t>
   </si>
   <si>
-    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als conditional reference dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als Conditional Reference dokumentiert.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -2003,9 +2003,6 @@
     <t>MedicationRequest.courseOfTherapyType.text</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
-  </si>
-  <si>
     <t>MedicationRequest.insurance</t>
   </si>
   <si>
@@ -2032,7 +2029,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zum Planeintrag.</t>
+    <t>Zusätzliche Informationen zum Planeintrag, die nicht die Dosierung betreffen.</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -17722,7 +17719,7 @@
         <v>104</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>637</v>
+        <v>391</v>
       </c>
       <c r="M128" t="s" s="2">
         <v>354</v>
@@ -17812,10 +17809,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17838,13 +17835,13 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17895,7 +17892,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -17910,13 +17907,13 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM129" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>21</v>
@@ -17927,10 +17924,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17953,13 +17950,13 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18010,7 +18007,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18025,13 +18022,13 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AL130" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AL130" t="s" s="2">
+      <c r="AM130" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>21</v>
@@ -18042,10 +18039,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18157,10 +18154,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18274,10 +18271,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18300,16 +18297,16 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18359,7 +18356,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18380,7 +18377,7 @@
         <v>21</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>21</v>
@@ -18391,10 +18388,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18420,10 +18417,10 @@
         <v>241</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18474,7 +18471,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18495,7 +18492,7 @@
         <v>21</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>21</v>
@@ -18506,10 +18503,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18535,10 +18532,10 @@
         <v>269</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18589,7 +18586,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>90</v>
@@ -18610,7 +18607,7 @@
         <v>21</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>21</v>
@@ -18621,10 +18618,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18647,16 +18644,16 @@
         <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18694,7 +18691,7 @@
         <v>21</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
@@ -18704,7 +18701,7 @@
         <v>409</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18719,13 +18716,13 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM136" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>21</v>
@@ -18736,13 +18733,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C137" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>21</v>
@@ -18764,16 +18761,16 @@
         <v>21</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18823,7 +18820,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18838,13 +18835,13 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM137" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
@@ -18855,13 +18852,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C138" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>21</v>
@@ -18883,16 +18880,16 @@
         <v>21</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18942,7 +18939,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -18954,16 +18951,16 @@
         <v>21</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AK138" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM138" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>21</v>
@@ -18974,10 +18971,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19000,13 +18997,13 @@
         <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="L139" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19057,7 +19054,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19075,10 +19072,10 @@
         <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AM139" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
@@ -19089,10 +19086,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19204,10 +19201,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19321,14 +19318,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19350,16 +19347,16 @@
         <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
@@ -19408,7 +19405,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19440,10 +19437,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19466,16 +19463,16 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19525,7 +19522,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19546,7 +19543,7 @@
         <v>21</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -19557,10 +19554,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19672,10 +19669,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19789,14 +19786,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -19818,16 +19815,16 @@
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>21</v>
@@ -19876,7 +19873,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19908,10 +19905,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19934,13 +19931,13 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19991,7 +19988,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20003,16 +20000,16 @@
         <v>21</v>
       </c>
       <c r="AJ147" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM147" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="AK147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL147" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM147" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>21</v>
@@ -20023,10 +20020,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20049,13 +20046,13 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20106,7 +20103,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20127,7 +20124,7 @@
         <v>21</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>21</v>
@@ -20138,10 +20135,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20164,13 +20161,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20221,7 +20218,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20242,7 +20239,7 @@
         <v>21</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>21</v>
@@ -20253,10 +20250,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20282,16 +20279,16 @@
         <v>231</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="N150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>21</v>
@@ -20340,7 +20337,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20358,10 +20355,10 @@
         <v>21</v>
       </c>
       <c r="AL150" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="AM150" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>21</v>
@@ -20372,10 +20369,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20398,16 +20395,16 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="L151" t="s" s="2">
+      <c r="M151" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20457,7 +20454,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20475,24 +20472,24 @@
         <v>21</v>
       </c>
       <c r="AL151" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AM151" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="AM151" t="s" s="2">
+      <c r="AN151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO151" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>735</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20515,13 +20512,13 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20572,7 +20569,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20584,30 +20581,30 @@
         <v>21</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL152" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="AM152" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="AM152" t="s" s="2">
+      <c r="AN152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO152" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>741</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20630,16 +20627,16 @@
         <v>21</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>743</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -20689,7 +20686,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20707,10 +20704,10 @@
         <v>21</v>
       </c>
       <c r="AL153" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="AM153" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>21</v>
@@ -20721,10 +20718,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20750,10 +20747,10 @@
         <v>509</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -20804,7 +20801,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -20825,7 +20822,7 @@
         <v>21</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>580</v>
@@ -20836,10 +20833,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20862,13 +20859,13 @@
         <v>21</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -20919,7 +20916,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -20937,10 +20934,10 @@
         <v>21</v>
       </c>
       <c r="AL155" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AM155" t="s" s="2">
         <v>755</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>756</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>21</v>
@@ -20951,10 +20948,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21066,10 +21063,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21183,14 +21180,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21212,16 +21209,16 @@
         <v>111</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>21</v>
@@ -21270,7 +21267,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21302,10 +21299,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21328,16 +21325,16 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="L159" t="s" s="2">
         <v>761</v>
       </c>
-      <c r="L159" t="s" s="2">
+      <c r="M159" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21366,11 +21363,11 @@
         <v>156</v>
       </c>
       <c r="Y159" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="Z159" t="s" s="2">
         <v>765</v>
       </c>
-      <c r="Z159" t="s" s="2">
-        <v>766</v>
-      </c>
       <c r="AA159" t="s" s="2">
         <v>21</v>
       </c>
@@ -21387,7 +21384,7 @@
         <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>90</v>
@@ -21405,24 +21402,24 @@
         <v>21</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AM159" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO159" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>768</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21448,10 +21445,10 @@
         <v>295</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21481,11 +21478,11 @@
         <v>156</v>
       </c>
       <c r="Y160" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="Z160" t="s" s="2">
         <v>772</v>
       </c>
-      <c r="Z160" t="s" s="2">
-        <v>773</v>
-      </c>
       <c r="AA160" t="s" s="2">
         <v>21</v>
       </c>
@@ -21502,7 +21499,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21520,24 +21517,24 @@
         <v>21</v>
       </c>
       <c r="AL160" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AM160" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="AM160" t="s" s="2">
+      <c r="AN160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO160" t="s" s="2">
         <v>775</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>776</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21560,13 +21557,13 @@
         <v>21</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21617,7 +21614,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21632,13 +21629,13 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AM161" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>21</v>
@@ -21649,14 +21646,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21675,16 +21672,16 @@
         <v>21</v>
       </c>
       <c r="K162" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="L162" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="L162" t="s" s="2">
+      <c r="M162" t="s" s="2">
         <v>786</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>788</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -21734,7 +21731,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21755,7 +21752,7 @@
         <v>21</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>21</v>
@@ -21766,10 +21763,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21792,16 +21789,16 @@
         <v>21</v>
       </c>
       <c r="K163" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="L163" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="L163" t="s" s="2">
+      <c r="M163" t="s" s="2">
         <v>792</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>793</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>794</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21851,7 +21848,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -21866,13 +21863,13 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AL163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM163" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="AL163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM163" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -643,7 +643,7 @@
 </t>
   </si>
   <si>
-    <t>TODO</t>
+    <t>Es sind nur die hier definierten contained Medication-Ressourcen zulässig. Contained (eingebettete) Ressourcen werden nicht separat versioniert, sondern ausschließlich im Rahmen der übergeordneten Ressource versioniert.</t>
   </si>
   <si>
     <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -836,7 +836,7 @@
 </t>
   </si>
   <si>
-    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definiert Regeln befüllt.</t>
+    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definierten Regeln befüllt..</t>
   </si>
   <si>
     <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1709,7 +1709,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole)
 </t>
   </si>
   <si>
@@ -2835,7 +2835,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="199.48828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="180.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -639,7 +639,7 @@
     <t>MedicationRequest.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung}
+    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-wirkstoff}
 </t>
   </si>
   <si>
@@ -1313,7 +1313,7 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-wirkstoff) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -2835,7 +2835,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="180.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="248.72265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil für einen Medikationsplaneintrag.</t>
+    <t>Profil für einen Planeintrag.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1685,7 +1685,7 @@
     <t>MedicationRequest.authoredOn</t>
   </si>
   <si>
-    <t>Datum der Erstellung des Planeintrags.</t>
+    <t>Datum der Erstellung/Änderung des Planeintrags.</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -568,7 +568,7 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
+    <t>Narrative - wird immer durch die Fachanwendung generiert.</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>90</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1313,7 +1313,7 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-wirkstoff) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-wirkstoff)
 </t>
   </si>
   <si>
@@ -2835,7 +2835,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="248.72265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="237.0078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -924,7 +924,7 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/PlaneintragStatusVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-planeintragstatus-vs</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -955,7 +955,7 @@
     <t>This is generally only used for "exception" statuses such as "suspended" or "cancelled". The reason why the MedicationRequest was created at all is captured in reasonCode, not here.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetPlaneintragStatusReasonVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-planeintrag-statusreason-vs</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1185,7 +1185,7 @@
     <t>The category can be used to include where the medication is expected to be consumed or other types of requests.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedicationRequestCategoryVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-medicationrequestcategory-vs</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -1219,7 +1219,7 @@
     <t>MedicationRequest.category.coding.system</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/at-elga-emed-codesystem-medicationrequestcategory-cs</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding.version</t>
@@ -1964,7 +1964,7 @@
     <t>This attribute should not be confused with the protocol of the medication.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetCourseOfTherapyType</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-medicationrequest-courseoftherapytype-vs</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -2850,7 +2850,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="104.39453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.75" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="85.7421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="50.23046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -836,7 +836,7 @@
 </t>
   </si>
   <si>
-    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definierten Regeln befüllt..</t>
+    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definierten Regeln befüllt.</t>
   </si>
   <si>
     <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>At ELGA e-Medikation MedicationRequest Planeintrag</t>
+    <t>AT ELGA e-Medikation MedicationRequest Planeintrag</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
